--- a/Con_Law_Outline_Week_8_with_Midterm_QA.xlsx
+++ b/Con_Law_Outline_Week_8_with_Midterm_QA.xlsx
@@ -12210,7 +12210,7 @@
       </c>
       <c r="C2" s="95" t="inlineStr">
         <is>
-          <t>Iredell accepted judicial review, but only to enforce the written Constitution, and only in a clear and urgent case. He rejected voiding laws for violating 'natural justice,' because natural-justice principles have no fixed standard and reasonable people disagree about them. D describes Justice Chase, who would let courts void laws contrary to 'first principles of the social compact' even without a specific textual provision. A is wrong because Iredell accepted the power. B invents a Tenth Amendment limit that neither Justice adopted.</t>
+          <t>Iredell accepted judicial review, but tied it to the written Constitution. A court may declare a legislative act void only when it clearly violates a particular constitutional provision, and only in a clear and urgent case. He refused to rest invalidation on 'natural justice,' because those principles have no fixed standard and the ablest people disagree about them.</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="C3" s="95" t="inlineStr">
         <is>
-          <t>Thomas argued the majority's holding (no concrete injury, so no Article III standing for most class members) didn't erase the statutory rights Congress created under the FCRA. Article III limits only federal courts. State courts aren't bound by federal justiciability rules, so plaintiffs can bring the same FCRA claims there. By closing the federal forum, the Court may have sent these class actions to state courts as the only forum, which is possibly worse for TransUnion. That's the 'pyrrhic victory.' A, B and C misdescribe the holding: it was a standing ruling, not a political-question or appellate-jurisdiction ruling, and Thomas's point wasn't about congressional override.</t>
+          <t>Thomas argued the majority's holding (no concrete injury, so no Article III standing for most class members) didn't erase the statutory rights Congress created under the FCRA. Article III limits only federal courts, and state courts aren't bound by federal justiciability rules. By closing the federal forum, the Court may have left state courts as the only forum for these class actions, and possibly a less favorable one for TransUnion. That's the 'pyrrhic victory.'</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="C4" s="95" t="inlineStr">
         <is>
-          <t>Seminole Tribe holds that Congress can't use its Article I powers, including the Commerce Clause, to abrogate state sovereign immunity. Allen v. Cooper applied the same rule to the Intellectual Property Clause. The exceptions are §5 of the Fourteenth Amendment (valid, congruent and proportional legislation) and the Bankruptcy Clause, where Katz found the states consented 'in the plan of the Convention.' A commerce-based trademark statute fits neither. A gets the rule backwards. B misapplies the plan-of-the-Convention reasoning, which Katz tied to bankruptcy. D is too broad because §5 abrogation is allowed.</t>
+          <t>Seminole Tribe holds that Congress can't use its Article I powers, including the Commerce Clause, to abrogate state sovereign immunity. Allen v. Cooper applied the same rule to the Intellectual Property Clause. The recognized routes are §5 of the Fourteenth Amendment and the Bankruptcy Clause (Katz, 'plan of the Convention'). A commerce-based trademark statute uses neither, so the abrogation is unconstitutional.</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="C5" s="95" t="inlineStr">
         <is>
-          <t>Under the aggregation principle (Wickard, Perez, Raich), Congress may regulate a class of activities that, taken together, substantially affects interstate commerce. Each individual instance doesn't need an interstate effect. Residential rentals are economic activity, and the rental market as a whole affects interstate commerce. Because the FAA reaches as far as the commerce power, the clause is likely enforceable. A and B look only at this one local transaction. C overstates the commerce power, which Lopez confirmed has limits and doesn't cover all intrastate commerce.</t>
+          <t>Under the aggregation principle (Wickard, Perez, Raich), Congress may regulate a class of economic activities that, taken together, substantially affects interstate commerce, even when an individual instance is local. Residential rentals are economic activity, and the rental market as a whole affects interstate commerce. Because the FAA reaches as far as the commerce power, the arbitration clause is likely enforceable.</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="C6" s="95" t="inlineStr">
         <is>
-          <t>A federal district court is bound by its own circuit's court of appeals (the Seventh Circuit for the Northern District of Illinois) and by the U.S. Supreme Court. District court decisions aren't binding precedent, even in the same district. The Illinois Supreme Court doesn't bind a federal court on a question of federal constitutional law. So only the Seventh Circuit, among the choices, is binding.</t>
+          <t>A federal district court is bound by the decisions of the court of appeals for its own circuit and by the U.S. Supreme Court. The Northern District of Illinois sits in the Seventh Circuit, so Seventh Circuit decisions bind it.</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="C8" s="95" t="inlineStr">
         <is>
-          <t>In Federalist No. 78, Hamilton argues the Constitution is fundamental law expressing the will of the people, superior to statutes reflecting the will of their agents. Where there's an irreconcilable variance, judges must prefer the Constitution to the statute. That doesn't make the judiciary superior to the legislature; it makes the people's will superior to both. A states the opposite. B invents an Article-by-Article split. D misreads the Founders' relationship to British legal traditions.</t>
+          <t>In Federalist No. 78, Hamilton argues the Constitution is fundamental law expressing the will of the people, superior to statutes, which reflect the will of the people's agents. When the two irreconcilably conflict, judges must prefer the Constitution. That doesn't make the judiciary superior to the legislature; it makes the people's will superior to both.</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="C9" s="95" t="inlineStr">
         <is>
-          <t>President Clinton responded by proposing to amend the Gun-Free School Zones Act to add a jurisdictional element, requiring that the firearm have moved in or otherwise affected interstate commerce. Congress did so in 1996 (amended 18 U.S.C. §922(q)), and courts later upheld the amended statute (e.g., United States v. Dorsey, 9th Cir. 2005).</t>
+          <t>President Clinton responded by proposing to amend the Gun-Free School Zones Act to add a jurisdictional element, requiring that the firearm have moved in or otherwise affected interstate commerce. That would bring the law within Congress's Commerce Clause authority. Congress enacted the amendment in 1996 (amended 18 U.S.C. §922(q)), and courts later upheld it (e.g., United States v. Dorsey, 9th Cir. 2005).</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="C10" s="95" t="inlineStr">
         <is>
-          <t>On a federal question, a state court is bound only by the U.S. Supreme Court (and by its own state's higher courts, which aren't among the choices). Lower federal courts, including the Central District of California and the Ninth Circuit, aren't above state courts. Their decisions are only persuasive in the Los Angeles County Superior Court, despite the geographic overlap.</t>
+          <t>On a question of federal law such as the First Amendment, a state court is bound by the U.S. Supreme Court, the final authority on federal constitutional questions. So a Supreme Court decision binds the Los Angeles County Superior Court.</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="C11" s="95" t="inlineStr">
         <is>
-          <t>Under Hans v. Louisiana, state sovereign immunity bars private damages suits against a nonconsenting state in federal court, whether the plaintiff is a citizen of that state or another. A damages claim against the program director that would be paid from the state treasury is really against the state (Edelman), so immunity applies. Congress didn't abrogate, and the statute is silent; abrogation requires an unmistakably clear statement and a valid source of power. B, C and D all treat the plaintiff's citizenship or the federal nature of the claim as decisive, but neither defeats immunity.</t>
+          <t>Under Hans v. Louisiana, state sovereign immunity bars private suits for damages against a nonconsenting state in federal court, including suits by the state's own citizens. A damages claim against the program director that would be paid from the state treasury is really a claim against the state (Edelman). The statute doesn't abrogate immunity, which requires an unmistakably clear statement and a valid source of power. So Illinois can claim sovereign immunity.</t>
         </is>
       </c>
     </row>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="C12" s="95" t="inlineStr">
         <is>
-          <t>Clapper v. Amnesty International: the plaintiffs' fear of surveillance rested on a 'highly attenuated chain of possibilities.' They couldn't show their communications were or would be intercepted, so the injury wasn't 'certainly impending.' Any interception also might occur under some other authority, so it wasn't fairly traceable to §1881a. They can't manufacture standing by spending money to avoid a speculative harm, which is why D fails. A goes to the merits, not standing. C invents an attorney exception.</t>
+          <t>Clapper v. Amnesty International: a threatened injury must be 'certainly impending.' The plaintiffs' fear of interception rested on a speculative chain of possibilities, so they couldn't show an injury in fact. Any interception also might occur under some other authority, so it wasn't fairly traceable to §1881a. Costs they chose to incur to avoid a speculative harm can't create standing.</t>
         </is>
       </c>
     </row>
@@ -12419,7 +12419,7 @@
       </c>
       <c r="C14" s="95" t="inlineStr">
         <is>
-          <t>Marshall read §13 as conferring original jurisdiction to issue mandamus, which created the conflict with Article III. But a plausible alternative reading (often noted by commentators) is that §13 simply authorized the Court to issue writs of mandamus, warranted by the principles and usages of law, in cases already properly before it. That's a remedial power, not a jurisdictional grant. On that reading, there would have been no constitutional conflict and no need for judicial review.</t>
+          <t>Section 13 can plausibly be read as simply authorizing the Supreme Court to issue writs of mandamus, warranted by the principles and usages of law, in cases already properly before it. That's a remedial power, not a jurisdictional grant. On that reading, §13 wouldn't add to the Court's original jurisdiction, and there would be no conflict with Article III.</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="C15" s="95" t="inlineStr">
         <is>
-          <t>A plaintiff need not expose himself to arrest or prosecution to challenge a law that deters constitutionally protected conduct. A credible threat of prosecution is enough (Steffel v. Thompson). Smith was twice warned, his companion was actually arrested and charged, and the parties stipulated he might be arrested. That's a concrete, particularized and sufficiently imminent injury. B demands certainty, which isn't required. C misapplies TransUnion's history test, since threatened prosecution is a traditionally recognized harm. D confuses widespread risk with a generalized grievance; Smith is personally threatened.</t>
+          <t>A plaintiff need not expose himself to arrest or prosecution to challenge a law that deters constitutionally protected conduct. A credible threat of prosecution is enough (Steffel v. Thompson). Smith was twice warned, his companion was actually arrested and charged, and the parties stipulated he might be arrested if he returned. That's a concrete, particularized and sufficiently imminent injury.</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="C16" s="95" t="inlineStr">
         <is>
-          <t>In 1793, the Washington Administration asked the Justices for legal advice on questions of treaty construction and international law. The Justices declined, citing separation of powers and the courts' role as a court of last resort deciding actual cases. This established the precedent against federal advisory opinions. B, C and D attach the episode to doctrines that developed separately.</t>
+          <t>In 1793, the Washington Administration asked the Justices for legal advice on questions of treaty construction and international law. The Justices declined, citing separation of powers and the courts' role in deciding actual cases. This established the precedent that federal courts don't issue advisory opinions.</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="C17" s="95" t="inlineStr">
         <is>
-          <t>Brutus, a leading Anti-Federalist, warned that the Constitution's general, indefinite language (for example, 'necessary and proper' and 'general welfare') would be construed by judges to expand federal power. He argued this would gradually swallow and effectively abolish the state governments. Because judges would be independent and their constitutional rulings final, the legislature couldn't correct or control them. All three criticisms appear in Brutus.</t>
+          <t>Brutus, a leading Anti-Federalist, made each of these criticisms. The Constitution's general, indefinite language would be construed by judges in favor of federal power. That expansion would gradually swallow and effectively abolish the state governments. And because judges would be independent and their constitutional rulings final, the legislature couldn't control or correct the Supreme Court.</t>
         </is>
       </c>
     </row>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="C18" s="95" t="inlineStr">
         <is>
-          <t>After Lopez, the most reliable way to keep a federal criminal statute within the Commerce Clause is a jurisdictional element requiring a case-by-case link to interstate commerce, such as a firearm that moved in interstate commerce. That's what Congress did when it amended §922(q), and courts upheld it (Dorsey). Findings and hearings help (C and B) but aren't dispositive; Morrison struck down VAWA's civil remedy despite extensive findings. A two-thirds majority (A) has no constitutional significance for enumerated power.</t>
+          <t>After Lopez, the most reliable way to keep a federal criminal statute within the Commerce Clause is a jurisdictional element requiring a case-specific link to interstate commerce, such as a firearm that moved in interstate commerce. Congress did exactly this when it amended §922(q) after Lopez, and courts upheld the amended statute (Dorsey).</t>
         </is>
       </c>
     </row>
@@ -12508,7 +12508,7 @@
       </c>
       <c r="C19" s="95" t="inlineStr">
         <is>
-          <t>Lopez identified three categories Congress may regulate: (1) the channels of interstate commerce, (2) the instrumentalities of interstate commerce and persons or things in it, and (3) activities that substantially affect interstate commerce. The effect must be substantial. The Court said formal findings are not required, although they can help a court evaluate the effect, so A and B are wrong. D is wrong because the Court decided the question on the merits.</t>
+          <t>Lopez identified three categories Congress may regulate under the Commerce Clause: (1) the channels of interstate commerce, (2) the instrumentalities of interstate commerce and persons or things in it, and (3) activities that substantially affect interstate commerce. For the third category, the effect must be substantial.</t>
         </is>
       </c>
     </row>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="C20" s="95" t="inlineStr">
         <is>
-          <t>Perez v. United States (1971) upheld the federal loan-sharking (extortionate credit) statute as applied to purely intrastate transactions. Congress could regulate the whole class of activity because extortionate credit, as a class, affects interstate commerce. Lopez discussed Perez approvingly and didn't question it. Loan sharking is economic activity, unlike gun possession in Lopez. A relies on the 'costs of crime and education' reasoning Lopez rejected. C misstates Lopez: findings aren't required. D misreads both the Tenth Amendment and the case law.</t>
+          <t>Perez v. United States (1971) upheld the federal loan-sharking (extortionate credit) statute as applied to purely intrastate transactions. Congress could regulate the whole class of activity because extortionate credit, as a class, affects interstate commerce. Lopez cited Perez with approval and didn't question it, and loan sharking is economic activity. So a federal ban on loan sharking in schools fits within Perez.</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="C21" s="95" t="inlineStr">
         <is>
-          <t>Lopez didn't overrule any prior Commerce Clause case. Chief Justice Rehnquist treated Wickard, Perez and the other New Deal-era cases as still good law, and distinguished them on the ground that they involved economic activity, while gun possession in a school zone isn't economic.</t>
+          <t>Lopez didn't overrule any prior Commerce Clause case. Chief Justice Rehnquist treated Wickard, Perez and the other post-1937 cases as good law, and distinguished them on the ground that they involved economic activity, while possessing a gun in a school zone isn't economic.</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="C22" s="95" t="inlineStr">
         <is>
-          <t>The Court adopted Hamilton's view of the spending power (United States v. Butler; Helvering v. Davis). The power to tax and spend for the general welfare is a separate power, not limited to carrying out the other enumerated powers. Congress gets broad deference on what serves the general welfare, so a national museum is plainly within the power. B is Madison's narrower view, which the Court rejected. A misstates the test: national benefit doesn't require equal benefit to every state. D invents a location limit.</t>
+          <t>The Court adopted Hamilton's view of the spending power (United States v. Butler; Helvering v. Davis). The power to tax and spend for the general welfare is a separate power, not limited to carrying out the other enumerated powers in Article I, §8. Courts defer broadly to Congress's judgment about what serves the general welfare, so appropriating money for a national museum is within the power.</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="C23" s="95" t="inlineStr">
         <is>
-          <t>Mootness is standing set in a time frame: a live controversy must exist throughout the litigation, not just at filing. After graduation, with no intent to re-enroll, the plaintiff no longer has a personal stake in injunctive relief against the university's athletics program, so the claim became moot. She sought no damages that could keep it alive. A confuses ripeness (too early) with mootness (too late). D ignores that standing at filing isn't enough. C has no basis.</t>
+          <t>Mootness requires a live controversy throughout the litigation, not just when the suit is filed. Once the plaintiff graduated with no intent to re-enroll, she no longer had a personal stake in an injunction governing the university's athletics program. She sought no damages that could keep the case alive, so the claim became moot.</t>
         </is>
       </c>
     </row>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="C24" s="95" t="inlineStr">
         <is>
-          <t>In Chisholm v. Georgia (1793), the Court held that Article III allowed a South Carolina citizen to sue Georgia in federal court without its consent, so Georgia had no immunity. The backlash produced the Eleventh Amendment (1795), which overturned Chisholm. B, C and D get the holding or the sequence backwards: Chisholm came before the Eleventh Amendment and rejected immunity.</t>
+          <t>In Chisholm v. Georgia (1793), the Court held that Article III allowed a South Carolina citizen to sue Georgia in federal court without its consent, so Georgia had no sovereign immunity. The decision provoked a strong backlash and led to the Eleventh Amendment (ratified 1795), which overturned Chisholm.</t>
         </is>
       </c>
     </row>

--- a/Con_Law_Outline_Week_8_with_Midterm_QA.xlsx
+++ b/Con_Law_Outline_Week_8_with_Midterm_QA.xlsx
@@ -22,9 +22,12 @@
     <sheet name="laws-statutes glossary" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Week 7 Class Notes" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Week 8 Reading Notes" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Midterm questions &amp; answers" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Week 1 Fact Bank" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Midterm questions &amp; answers" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Week 1 Fact Bank'!$A$1:$F$164</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -32,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -98,8 +101,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="44">
+  <fills count="46">
     <fill>
       <patternFill/>
     </fill>
@@ -314,6 +321,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -563,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -838,6 +855,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12172,6 +12195,4951 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F164"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="75" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="96" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="96" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="C1" s="96" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="D1" s="96" t="inlineStr">
+        <is>
+          <t>Question (cover this column)</t>
+        </is>
+      </c>
+      <c r="E1" s="96" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="F1" s="96" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Year the Articles of Confederation were ratified?</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>1781 (ratified by the states Feb. 2, 1781; in effect Mar. 1, 1781 to Mar. 3, 1789).</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>When did Shays' Rebellion begin and end?</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Began 1786; ended February 1787.</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>When was the Constitutional Convention, and when did The Federalist begin publication?</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Convention in Philadelphia, May to September 1787. The Federalist began publication in October 1787.</t>
+        </is>
+      </c>
+      <c r="F4" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>When did the federal government begin operating, and when was the Judiciary Act of 1789 enacted?</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Government began March 4, 1789. Judiciary Act of 1789: September 24, 1789.</t>
+        </is>
+      </c>
+      <c r="F5" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>What two events does the timeline list for 1791?</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Congress charters the First Bank of the United States; Bill of Rights ratified.</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Who won the 1800 presidential election, and whom did he defeat?</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson, defeating incumbent John Adams.</t>
+        </is>
+      </c>
+      <c r="F7" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>When did John Marshall become Chief Justice, and which Chief Justice was he?</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>1801; the fourth Chief Justice.</t>
+        </is>
+      </c>
+      <c r="F8" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>What happened in 1804?</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Alexander Hamilton was killed in a duel with Aaron Burr.</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>First Bank charter expires / Second Bank chartered / McCulloch / Gibbons / Barron: years?</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>1811 / 1816 / 1819 / 1824 / 1833.</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Years of the 13th, 14th, 15th and 17th Amendments?</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>13th 1865; 14th 1868; 15th 1870; 17th 1913.</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Years of the Civil Rights Cases, Lochner, the "switch in time," Wickard and Youngstown?</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>1883; 1905; 1937; 1942; 1952.</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Years of the War Powers Resolution, INS v. Chadha, Lopez and Printz?</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>1973; 1983; 1995; 1997.</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Years of Trump v. United States and Trump v. Slaughter?</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>2024 and 2026.</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Declaration of Independence (July 4, 1776)</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Per the Declaration, from what do governments derive their just powers?</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>"from the consent of the governed."</t>
+        </is>
+      </c>
+      <c r="F15" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Declaration of Independence (July 4, 1776)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>What unalienable rights does the Declaration name?</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>"Life, Liberty and the pursuit of Happiness."</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Declaration of Independence (July 4, 1776)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>What right do the people have when a government becomes destructive of its ends?</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>"to alter or to abolish it, and to institute new Government." After "a long train of abuses and usurpations," it is their right and duty to throw off such government.</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Articles of Confederation</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Articles, Art. II: what does each state retain?</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Its sovereignty, freedom and independence, and every power, jurisdiction and right not "expressly delegated" to the United States in Congress assembled.</t>
+        </is>
+      </c>
+      <c r="F18" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Articles of Confederation</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Articles, Art. III: how do the states describe their relationship?</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>"a firm league of friendship with each other" for common defense, security of liberties, and mutual and general welfare.</t>
+        </is>
+      </c>
+      <c r="F19" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Articles of Confederation</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Articles: delegates per state, term limit, and votes per state in Congress?</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>No fewer than 2 and no more than 7 delegates; no one may serve more than 3 years in any 6; each state has ONE vote.</t>
+        </is>
+      </c>
+      <c r="F20" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Articles of Confederation</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Articles, Art. VIII: how was the common treasury funded?</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>By the states, in proportion to the value of land within each state; the taxes were laid and levied by the STATE legislatures.</t>
+        </is>
+      </c>
+      <c r="F21" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Articles of Confederation</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Articles, Art. IX: how many states had to assent to war, treaties, coining money, borrowing, appropriating, etc.?</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Nine states.</t>
+        </is>
+      </c>
+      <c r="F22" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Articles of Confederation</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Articles, Art. XIII: what did amending the Articles require?</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Agreement in Congress, then confirmation by the legislatures of EVERY state (unanimity). The union was to be "perpetual."</t>
+        </is>
+      </c>
+      <c r="F23" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 1 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Who wrote Federalist No. 1, under what name, and when?</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Alexander Hamilton, as "Publius," October 27, 1787.</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 1 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 1: what "important question" is reserved to the American people?</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Whether societies of men can establish good government "from reflection and choice," or are forever destined to depend on "accident and force."</t>
+        </is>
+      </c>
+      <c r="F25" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 15 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Who wrote Federalist No. 15, and when?</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Alexander Hamilton, December 1, 1787.</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 15 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 15: the "great and radical vice" of the Confederation?</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>LEGISLATION for STATES or GOVERNMENTS in their CORPORATE or COLLECTIVE capacities, as opposed to the INDIVIDUALS who compose them.</t>
+        </is>
+      </c>
+      <c r="F27" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 15 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 15: why are the Confederation's requisitions "mere recommendations"?</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Congress could requisition men and money but had no authority to raise either by regulations reaching individual citizens, so states observed or disregarded them at their option.</t>
+        </is>
+      </c>
+      <c r="F28" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 15 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 15: the two ways to enforce a law's sanction?</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Coercion of the magistracy (courts; applies only to men) or coercion of arms (military force; the only way to act against states). Legislating for states means every breach is a state of war.</t>
+        </is>
+      </c>
+      <c r="F29" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 15 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 15: whose concurrence was needed to execute every important Union measure?</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>"thirteen distinct sovereign wills."</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 84 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Who wrote Federalist No. 84, and when (per the reader)?</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Alexander Hamilton, May 28, 1788.</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 84 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 84: Hamilton's position on a bill of rights?</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Unnecessary AND dangerous: it would contain exceptions to powers not granted, giving a "colourable pretext" to claim more power than was granted.</t>
+        </is>
+      </c>
+      <c r="F32" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 84 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 84: what example does Hamilton use, and where does he say its security ultimately rests?</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Liberty of the press. "Why declare that things shall not be done which there is no power to do?" Its security depends on public opinion and the general spirit of the people and government.</t>
+        </is>
+      </c>
+      <c r="F33" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 1</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Who was Brutus, where and when did Brutus No. 1 appear?</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Melancton Smith or Robert Yates; New York Journal, October 18, 1787.</t>
+        </is>
+      </c>
+      <c r="F34" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 1</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 1: the first question, and his answer?</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Whether a confederated government is best, or the 13 states should be reduced to one great republic. The Constitution approaches so near "consolidation" that it must "certainly and infallibly terminate in it."</t>
+        </is>
+      </c>
+      <c r="F35" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 45 (Madison)</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Who wrote Federalist No. 45, and when?</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>James Madison, January 26, 1788.</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 45 (Madison)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 45: federal vs. state powers?</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Federal powers are "few and defined"; state powers are "numerous and indefinite."</t>
+        </is>
+      </c>
+      <c r="F37" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 45 (Madison)</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 45: on what objects will federal powers mainly operate, and state powers?</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Federal: external objects (war, peace, negotiation, foreign commerce, with taxation connected). States: lives, liberties and properties of the people, and internal order and prosperity.</t>
+        </is>
+      </c>
+      <c r="F38" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 45 (Madison)</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 45: the new Constitution's change consists less in __ than in __?</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Less in the addition of NEW POWERS than in the invigoration of ORIGINAL POWERS. The one new power named: regulation of commerce, which few oppose.</t>
+        </is>
+      </c>
+      <c r="F39" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 45 (Madison)</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 45: when will federal vs. state governments be most important?</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Federal in times of war and danger; states in times of peace and security.</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 47 (Madison)</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 47 (Madison, Jan. 30, 1788): what is "the very definition of tyranny"?</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>The accumulation of all powers, legislative, executive and judiciary, in the same hands, whether of one, a few or many, hereditary, self-appointed or elective.</t>
+        </is>
+      </c>
+      <c r="F41" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Who wrote Federalist No. 51, and when?</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>James Madison, February 6, 1788.</t>
+        </is>
+      </c>
+      <c r="F42" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: how is the partition of power maintained, since "exterior provisions" are inadequate?</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>By contriving the INTERIOR structure of government so its parts, by their mutual relations, keep each other in their proper places.</t>
+        </is>
+      </c>
+      <c r="F43" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: why does Madison relax the "same fountain of authority" principle for the judiciary?</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>(1) Peculiar qualifications are essential, so choose the mode that best secures them; (2) permanent tenure soon destroys any sense of dependence on the appointing authority.</t>
+        </is>
+      </c>
+      <c r="F44" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: the "great security" against concentration of power?</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Giving each department the constitutional means and personal motives to resist encroachment. "Ambition must be made to counteract ambition."</t>
+        </is>
+      </c>
+      <c r="F45" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: complete "If men were angels..."</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>"...no government would be necessary. If angels were to govern men, neither external nor internal controuls on government would be necessary."</t>
+        </is>
+      </c>
+      <c r="F46" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: the "great difficulty" in framing a government of men over men?</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>First enable the government to control the governed; then oblige it to control itself. Dependence on the people is the primary control, plus "auxiliary precautions."</t>
+        </is>
+      </c>
+      <c r="F47" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: which branch predominates in a republic, and the remedy?</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>The legislature. Remedy: divide it into branches with different modes of election and principles of action. The weaker executive should be fortified.</t>
+        </is>
+      </c>
+      <c r="F48" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: why is an absolute executive veto ("absolute negative") not enough?</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Ordinarily it might not be exerted with firmness; in extraordinary cases it might be perfidiously abused. Madison suggests a qualified connection with the weaker branch of the legislature (Senate).</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: what is the "double security"?</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>In the compound republic, power is first divided between two governments (federal and state), then each portion is subdivided among separate departments. The governments control each other while each controls itself.</t>
+        </is>
+      </c>
+      <c r="F50" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: two ways to protect the minority from a majority faction, and which America uses?</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>(1) A will independent of society (hereditary/self-appointed: precarious); (2) so many separate interests that an unjust majority combination is improbable. America uses the second, the extended republic.</t>
+        </is>
+      </c>
+      <c r="F51" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: civil rights are secured like religious rights, by what?</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>Multiplicity of interests, like multiplicity of sects. Security grows with the extent of territory and number of people.</t>
+        </is>
+      </c>
+      <c r="F52" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: which state does Madison use as his example of factious majority oppression?</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>Rhode Island (if separated from the confederacy and left to itself).</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 51 (Madison)</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 51: "____ is the end of government."</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Justice. "It is the end of civil society."</t>
+        </is>
+      </c>
+      <c r="F54" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Who wrote the "Modes of Constitutional Interpretation" reading?</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Brandon J. Murrill, Legislative Attorney, Congressional Research Service Report R45129 (updated March 15, 2018).</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Name the eight modes of constitutional interpretation in the CRS report.</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>Textualism; Original Meaning; Judicial Precedent; Pragmatism; Moral Reasoning; National Identity ("Ethos"); Structuralism; Historical Practices.</t>
+        </is>
+      </c>
+      <c r="F56" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>Textualism (CRS)?</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>Plain meaning of the text, usually as understood at ratification and in context; typically does not inquire into drafters' or ratifiers' intent.</t>
+        </is>
+      </c>
+      <c r="F57" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Original Meaning (CRS)? How does it differ from textualism?</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>The Constitution's meaning as understood by at least some segment of the populace at the Founding; that "objectively identifiable" public meaning hasn't changed. Textualism looks solely at the text.</t>
+        </is>
+      </c>
+      <c r="F58" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>According to CRS, what is "the most commonly cited source of constitutional meaning"?</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>Judicial precedent (the Supreme Court's prior decisions).</t>
+        </is>
+      </c>
+      <c r="F59" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Pragmatism (CRS)?</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Weighing the probable practical consequences of competing interpretations (costs and benefits), or considering whether the judiciary can play a constructive role in deciding the question.</t>
+        </is>
+      </c>
+      <c r="F60" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>Moral Reasoning (CRS)?</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>Moral concepts underlie certain terms (e.g., "equal protection," "due process of law") and should inform interpretation.</t>
+        </is>
+      </c>
+      <c r="F61" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>National Identity / "Ethos" (CRS)?</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>Relies on the distinct character and values of American national identity and institutions.</t>
+        </is>
+      </c>
+      <c r="F62" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Structuralism (CRS)?</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>Inferences from the Constitution's design: relations among the three branches (separation of powers), federal-state (federalism), and government-people.</t>
+        </is>
+      </c>
+      <c r="F63" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Modes</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Historical Practices (CRS)?</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>Long-established practices of the political branches as a source of meaning, especially in separation of powers, federalism and individual rights when the text is unclear.</t>
+        </is>
+      </c>
+      <c r="F64" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Professor's note</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull: what does the professor say to focus on (and not)?</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>NOT the holding (Ex Post Facto Clause, not a Con Law I topic). Focus on the dicta in Justice Chase's and Justice Iredell's opinions about constitutional interpretation, the courts' role, and unenumerated rights.</t>
+        </is>
+      </c>
+      <c r="F65" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>How did the Court deliver its opinions in Calder, and who was absent?</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>Seriatim (each justice separately). Argued in the absence of the Chief Justice. Opinions by Chase, Paterson, Iredell and Cushing.</t>
+        </is>
+      </c>
+      <c r="F66" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull: what did the Connecticut legislature do?</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>Passed a resolution setting aside a probate court decree (which had disapproved Normand Morrison's will) and granting a new hearing; on rehearing the will was approved. Calder and wife lost; Bull and wife won.</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Chase</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>Chase in Calder: is a state legislature omnipotent?</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>No. Even without express limits, "certain vital principles in our free Republican governments" overrule flagrant abuse. An act contrary to the "great first principles of the social compact" is not a rightful exercise of legislative authority.</t>
+        </is>
+      </c>
+      <c r="F68" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>Chase</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>Chase in Calder: his four examples of acts a legislature cannot do?</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>(1) Punish a citizen for an act innocent when done; (2) destroy or impair lawful private contracts; (3) make a man judge in his own cause; (4) take property from A and give it to B.</t>
+        </is>
+      </c>
+      <c r="F69" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Chase</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Chase in Calder: what does he call the view that legislatures have such powers unless expressly restrained?</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>"a political heresy, altogether inadmissible in our free republican governments."</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Chase</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>Chase in Calder: when would he declare a law void?</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>Only "in a very clear case."</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Iredell</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>Iredell in Calder: can a court void a law merely because it violates natural justice?</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>No. Courts may void acts violating constitutional provisions (but only in a "clear and urgent case"). They cannot void a law within the legislature's constitutional power merely because it is contrary to natural justice.</t>
+        </is>
+      </c>
+      <c r="F72" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>Iredell</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>Iredell in Calder: why not enforce natural justice?</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>"The ideas of natural justice are regulated by no fixed standard: the ablest and the purest men have differed upon the subject."</t>
+        </is>
+      </c>
+      <c r="F73" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Iredell</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>Chase vs. Iredell in one line?</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>Chase: courts may enforce unwritten first principles (unenumerated rights). Iredell: only written constitutional limits.</t>
+        </is>
+      </c>
+      <c r="F74" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Martineau, Society in America (1837)</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>Harriet Martineau (1837): her criticism of life-tenured judges?</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>Life appointment departs from the republican principle; theirs is a "virtually irresponsible office," and "irresponsible offices are an inconsistency in a republic."</t>
+        </is>
+      </c>
+      <c r="F75" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>Martineau, Society in America (1837)</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>Martineau: how republican is each body?</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>House: mainly republican. Senate: only partially (members not elected immediately by the people). Judiciary: "not republican at all."</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>Organization of federal courts / binding authority</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>The federal court system has how many courts of appeals and district courts? Which circuit is Illinois in?</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>13 courts of appeals; 94 district courts; Illinois is in the Seventh Circuit.</t>
+        </is>
+      </c>
+      <c r="F77" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>Organization of federal courts / binding authority</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Rule 1</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>Rule 1: Supreme Court decisions are binding until when? (Key quotes)</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>Until overruled by the Supreme Court itself. Hohn: precedents bind "until we see fit to reconsider them." Rodriguez de Quijas: lower courts follow the directly controlling case and leave overruling to the Court.</t>
+        </is>
+      </c>
+      <c r="F78" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Organization of federal courts / binding authority</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Rule 1</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>Exception to Rule 1 for statutory decisions?</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>When Congress amends the statute the Court interpreted, the decision no longer applies (Rivers v. Roadway Express; Agri Processor (D.C. Cir.)).</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Organization of federal courts / binding authority</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Rule 2</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>Rule 2: whom do courts of appeals decisions bind?</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Federal district courts within their circuits. Glaser (7th Cir.): "Nothing the eighth circuit decides is 'binding' on district courts outside its territory"; other circuits get "respectful consideration."</t>
+        </is>
+      </c>
+      <c r="F80" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>Organization of federal courts / binding authority</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Rule 3</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>Rule 3: are district court decisions binding?</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>No, not even in the same district or on the same judge in a different case (Camreta v. Greene; Articles of Drug... 203 Paper Bags (7th Cir.)).</t>
+        </is>
+      </c>
+      <c r="F81" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>Organization of federal courts / binding authority</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>Rule 4</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>Rule 4: are federal decisions binding on state courts?</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>Supreme Court decisions on federal law bind state courts; lower federal court decisions do not (persuasive only). Illinois Supreme Court has been inconsistent (Sprietsma).</t>
+        </is>
+      </c>
+      <c r="F82" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11: author and date?</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>Melancton Smith (or Robert Yates), New York Journal, January 31, 1788.</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11: why must "cases arising under this constitution" differ from cases under the laws?</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>Otherwise the two clauses mean exactly the same thing. They include cases requiring explanation of the nature and extent of the departments' powers, so judges get power to construe the Constitution.</t>
+        </is>
+      </c>
+      <c r="F84" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11: how will courts construe the Constitution, and who can correct them?</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>Not by fixed rules but by its "reason and spirit." No power can correct their errors; from this court "there is no appeal," and the legislature cannot set aside its judgments.</t>
+        </is>
+      </c>
+      <c r="F85" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11: what will the judicial power effect "in the most certain, but yet silent and imperceptible manner"?</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>An entire subversion of the legislative, executive and judicial powers of the individual states.</t>
+        </is>
+      </c>
+      <c r="F86" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 11: two reasons courts will favor extending federal power?</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>(1) The Constitution invites it: general, indefinite terms, the necessary and proper clause, and the preamble's ends justify an "equitable construction." (2) Judges' self-interest in enlarging their own power, dignity and pay.</t>
+        </is>
+      </c>
+      <c r="F87" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15: date?</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>March 20, 1788 (New York Journal).</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15: the Supreme Court will be what?</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>"exalted above all other power in the government, and subject to no controul" - immense powers yet little responsibility.</t>
+        </is>
+      </c>
+      <c r="F89" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15: the English comparison?</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>English judges' decisions can be set aside by the House of Lords, and Parliament can pass a new law explaining a former one. No such power here: "The judges are supreme."</t>
+        </is>
+      </c>
+      <c r="F90" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15: how will courts abolish the states?</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>Gradually, "by insensible degrees," through cases between individuals the public barely notices, each precedent building on the last.</t>
+        </is>
+      </c>
+      <c r="F91" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>Brutus No. 15: who should have the final say on constitutional meaning, and why?</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>The legislature, because the people can remove legislators at elections. Judges independent of the people can be checked only "with a high hand and an outstretched arm."</t>
+        </is>
+      </c>
+      <c r="F92" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>Author/date</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>Who wrote Federalist No. 78, and the date given in the reader?</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>Alexander Hamilton; May 28, 1788.</t>
+        </is>
+      </c>
+      <c r="F93" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: the three topics of "the manner of constituting" the judiciary?</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>(1) Mode of appointing judges; (2) tenure; (3) partition of judicial authority among courts.</t>
+        </is>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: which branch is "least dangerous," and why?</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>The judiciary. The executive holds the sword; the legislature commands the purse. The judiciary has "neither FORCE nor WILL, but merely judgment" and depends on the executive to give effect to its judgments.</t>
+        </is>
+      </c>
+      <c r="F95" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: what tenure for judges, and why?</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>"During good behavior." Permanency in office is the "citadel of the public justice and the public security," protecting the weakest branch from being overpowered or awed.</t>
+        </is>
+      </c>
+      <c r="F96" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: what is a "limited Constitution," and how are its limits preserved?</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>One with specified exceptions to legislative authority (e.g., no bills of attainder, no ex post facto laws). Limits are preserved only through courts declaring contrary acts void.</t>
+        </is>
+      </c>
+      <c r="F97" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: the agency argument for judicial review?</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>Every act of a delegated authority contrary to its commission is void. Denying this would affirm "that the deputy is greater than his principal; that the servant is above his master."</t>
+        </is>
+      </c>
+      <c r="F98" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: does judicial review make the judiciary superior to the legislature?</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>No. It supposes only that the power of the PEOPLE is superior to both. Courts are an "intermediate body between the people and the legislature."</t>
+        </is>
+      </c>
+      <c r="F99" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: the rule for conflicting statutes vs. statute and Constitution?</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>Between equal authorities, the later in time prevails. Between superior and subordinate, the converse: the prior act of the superior (the Constitution) prevails.</t>
+        </is>
+      </c>
+      <c r="F100" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: WILL vs. JUDGMENT?</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t>"The courts must declare the sense of the law; and if they should be disposed to exercise WILL instead of JUDGMENT," they would substitute their pleasure for the legislature's.</t>
+        </is>
+      </c>
+      <c r="F101" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: why would periodic appointments be fatal?</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>If by the executive or legislature: complaisance to that branch; if both: unwillingness to displease either; if the people: too great a disposition to consult popularity.</t>
+        </is>
+      </c>
+      <c r="F102" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>The Federalist No. 78 (Hamilton)</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>Federalist No. 78: the "weightier reason" for permanent tenure?</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>Required qualifications: a voluminous code of laws and precedents takes long study, so few people have the skill, and fewer combine it with integrity.</t>
+        </is>
+      </c>
+      <c r="F103" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>1789 Act</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Act of 1789: size of the Supreme Court and quorum?</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>A chief justice and five associate justices (six); any four a quorum; two sessions (February and August).</t>
+        </is>
+      </c>
+      <c r="F104" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>1789 Act</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Act of 1789, Sec. 13: to whom could the Supreme Court issue writs of mandamus?</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>"in cases warranted by the principles and usages of law, to any courts appointed, or persons holding office, under the authority of the United States."</t>
+        </is>
+      </c>
+      <c r="F105" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>1789 Act</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Act of 1789, Sec. 25: what did it authorize?</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>Supreme Court review (by writ of error) of final judgments of a state's highest court that rejected a federal treaty, statute or authority, upheld a state law against a federal challenge, or denied a claimed federal right.</t>
+        </is>
+      </c>
+      <c r="F106" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>1789 Act</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Act of 1789, Sec. 14: habeas corpus?</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t>Federal courts may issue habeas and other writs necessary for their jurisdiction. Justices and district judges may grant habeas to inquire into the cause of commitment, but not for prisoners in jail unless in federal custody, committed for trial in federal court, or needed to testify.</t>
+        </is>
+      </c>
+      <c r="F107" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>1801 Act</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Act of 1801 (Feb. 13, 1801): Supreme Court size change?</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t>At the next vacancy, the Court would shrink to five justices (one chief, four associates). Sessions moved to June and December.</t>
+        </is>
+      </c>
+      <c r="F108" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>1801 Act</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Act of 1801: circuits and circuit judges?</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t>Six circuits; three circuit judges in each except the sixth. Circuit courts got federal-question jurisdiction ("arising under the constitution and laws") and cases over $400.</t>
+        </is>
+      </c>
+      <c r="F109" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>D.C. Act</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>Act Concerning the District of Columbia (Feb. 27, 1801): what laws applied and what counties were formed?</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>Virginia and Maryland law continued in the parts each ceded. Two counties: Washington (east of the Potomac) and Alexandria (west).</t>
+        </is>
+      </c>
+      <c r="F110" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>D.C. Act</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>D.C. Act, Sec. 11: justices of the peace?</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t>As many as the President thinks expedient, appointed for each county, to serve FIVE years.</t>
+        </is>
+      </c>
+      <c r="F111" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act; Repeal Act of 1802</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>Repeal</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>What did the Act of March 8, 1802 do, and what survived?</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>Repealed the Judiciary Act of 1801 (effective July 1). It did NOT repeal the D.C. Act, so the D.C. Circuit Court and the justice-of-the-peace positions survived.</t>
+        </is>
+      </c>
+      <c r="F112" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison: citation and decision date?</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>5 U.S. 137, February 24, 1803. Opinion by Chief Justice Marshall.</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>In what court did Marbury begin, and how?</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>In the Supreme Court itself: at the December 1801 term, the applicants moved for a rule ordering Secretary of State James Madison to show cause why a mandamus should not issue.</t>
+        </is>
+      </c>
+      <c r="F114" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>Who were the four applicants in Marbury, and who was their counsel?</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t>William Marbury, Dennis Ramsay, Robert Townsend Hooe and William Harper. Counsel: Charles Lee, former Attorney General.</t>
+        </is>
+      </c>
+      <c r="F115" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>What office and commission did Marbury seek?</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>Justice of the peace for the county of Washington in the District of Columbia (five-year term under the D.C. Act of Feb. 1801).</t>
+        </is>
+      </c>
+      <c r="F116" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: what did the Senate do when asked for extracts from its executive journal?</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>Denied the request and rejected the petition.</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: who was Levi Lincoln, and what did the Court rule about his testimony?</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>The Attorney General, who had been acting Secretary of State when the events happened. The Court held he was not bound to say what became of the commissions.</t>
+        </is>
+      </c>
+      <c r="F118" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: what did James Marshall's affidavit say?</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>On March 4, 1801, fearing riotous proceedings in Alexandria, he picked up about 12 commissions, couldn't carry them all, and returned several, including those for Hooe and Harper.</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: Marshall's three questions, in order?</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>(1) Does the applicant have a right to the commission? (2) If so, do the laws afford a remedy? (3) If so, is it a mandamus issuing from this court?</t>
+        </is>
+      </c>
+      <c r="F120" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: the three distinct operations in an appointment?</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>(1) Nomination: the President's sole, voluntary act. (2) Appointment: also voluntary, with Senate advice and consent. (3) Commission: arguably a constitutional duty ("He shall commission all the officers").</t>
+        </is>
+      </c>
+      <c r="F121" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: when is the appointment made, and when is the commission complete?</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>Appointment: when the President signs the commission (his last act). Commission complete: when the Secretary of State affixes the seal. Delivery is not required.</t>
+        </is>
+      </c>
+      <c r="F122" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="14" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: why couldn't the appointment be revoked?</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>The law gave a five-year term independent of the executive (not removable at will), so the appointment vested a legal right.</t>
+        </is>
+      </c>
+      <c r="F123" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: "The government of the United States has been emphatically termed..."</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>"...a government of laws, and not of men." It would not deserve that name if the laws furnished no remedy for violation of a vested legal right.</t>
+        </is>
+      </c>
+      <c r="F124" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: which executive acts are examinable in court?</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>Political/discretionary acts (officer as the President's "mere organ") are only politically examinable. Where law assigns a specific duty and individual rights depend on it, the injured person may resort to the courts.</t>
+        </is>
+      </c>
+      <c r="F125" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: whose definition of mandamus does Marshall quote?</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>Blackstone (3 Commentaries 110): a command from King's Bench requiring a person to do a particular thing appertaining to his office and duty. He also cites Lord Mansfield.</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: what determines whether mandamus may issue to a department head?</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>"Not by the office of the person to whom the writ is directed, but the nature of the thing to be done." Example: a recorded paper a copy of which the law gives for ten cents.</t>
+        </is>
+      </c>
+      <c r="F127" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>Jurisdiction</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: which statute authorized the mandamus, and why was it unconstitutional?</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>Sec. 13 of the Judiciary Act of 1789. Art. III gives original jurisdiction only where ambassadors, public ministers and consuls are affected or a state is a party; issuing mandamus to an officer is original, not appellate, jurisdiction.</t>
+        </is>
+      </c>
+      <c r="F128" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>Jurisdiction</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: Marshall's interpretive argument on original jurisdiction?</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
+        <is>
+          <t>Otherwise the distribution would be "mere surplusage." "It cannot be presumed that any clause in the constitution is intended to be without effect." Affirmative words can be negative of other objects.</t>
+        </is>
+      </c>
+      <c r="F129" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>Jurisdiction</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: the "essential criterion" of appellate jurisdiction?</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>It revises and corrects proceedings in a cause already instituted, and does not create that cause.</t>
+        </is>
+      </c>
+      <c r="F130" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>Judicial review</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: "It is emphatically the province and duty of the judicial department..."</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>"...to say what the law is." If two laws conflict, courts must decide on the operation of each.</t>
+        </is>
+      </c>
+      <c r="F131" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>Judicial review</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: the Constitution is either __ or __?</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t>Either "a superior, paramount law, unchangeable by ordinary means," or on a level with ordinary acts. If the latter, written constitutions are "absurd attempts...to limit a power in its own nature illimitable."</t>
+        </is>
+      </c>
+      <c r="F132" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>Judicial review</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: what does Marshall call a written constitution?</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
+        <is>
+          <t>"the greatest improvement on political institutions."</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C134" s="14" t="inlineStr">
+        <is>
+          <t>Judicial review</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: textual examples supporting judicial review?</t>
+        </is>
+      </c>
+      <c r="E134" s="14" t="inlineStr">
+        <is>
+          <t>"Arising under this constitution"; the treason clause (two witnesses to the same overt act, or confession in open court); the judicial oath; the Supremacy Clause lists the Constitution first and only laws "made in pursuance" of it.</t>
+        </is>
+      </c>
+      <c r="F134" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>Marbury: the final disposition?</t>
+        </is>
+      </c>
+      <c r="E135" s="14" t="inlineStr">
+        <is>
+          <t>"The rule must be discharged." Marbury had a right and a remedy, but the Court lacked jurisdiction to issue the mandamus.</t>
+        </is>
+      </c>
+      <c r="F135" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>Howard Lee McBain (1928): his critique of Marbury?</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t>Columbia professor and later dean, in The Living Constitution. The nub: "who shall determine what the constitution means?" Why assume Congress has less intelligence or respect for the Constitution than courts?</t>
+        </is>
+      </c>
+      <c r="F136" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>Central question</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle: central question (FJC)?</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="inlineStr">
+        <is>
+          <t>Could Congress remove a pending appeal from the Supreme Court's jurisdiction?</t>
+        </is>
+      </c>
+      <c r="F137" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>Military Reconstruction Act of 1867: what did it do, and what did President Johnson do?</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="inlineStr">
+        <is>
+          <t>Divided the former Confederate states except Tennessee into five military districts under Northern officers. Johnson vetoed it; Congress overrode.</t>
+        </is>
+      </c>
+      <c r="F138" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="14" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>What happened to the Mississippi and Georgia suits against enforcing the Reconstruction Act?</t>
+        </is>
+      </c>
+      <c r="E139" s="14" t="inlineStr">
+        <is>
+          <t>Dismissed as seeking abstract opinions on political matters. Justice Samuel Nelson said such questions might be decided "in a proper case with proper parties."</t>
+        </is>
+      </c>
+      <c r="F139" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte Milligan (1866): holding, and why it worried Republicans?</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>Military authorities in Indiana could not try civilians where civilian courts were operating, which suggested military rule in the South was improper.</t>
+        </is>
+      </c>
+      <c r="F140" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>Who was William McCardle, and why was he arrested?</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="inlineStr">
+        <is>
+          <t>A Mississippi newspaper editor who wrote inflammatory articles against the military officers (fall 1867). Arrested Nov. 8, 1867 for disturbing the peace, impeding the right to vote, libel and inciting insurrection; ordered tried by military commission.</t>
+        </is>
+      </c>
+      <c r="F141" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="14" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>Which court first heard McCardle's habeas petition, and who decided it?</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="inlineStr">
+        <is>
+          <t>U.S. Circuit Court for the Southern District of Mississippi. District Judge Robert Hill sat alone, held the detention legal, and released McCardle on bail pending appeal.</t>
+        </is>
+      </c>
+      <c r="F142" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="14" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>Why did no Supreme Court justice sit on McCardle's circuit court?</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
+          <t>Chief Justice Salmon P. Chase argued justices could not appear subordinate to military officials, so justices did not "ride circuit" in the South early in Reconstruction.</t>
+        </is>
+      </c>
+      <c r="F143" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="14" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr">
+        <is>
+          <t>Statute</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>Habeas Corpus Act of 1867 (Feb. 5, 1867): what did it do, and its purpose?</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>Expanded habeas to anyone restrained in violation of the Constitution, treaties or federal law, and allowed appeals to the Supreme Court. Purpose: let freedpeople secure their liberty against unfair state courts.</t>
+        </is>
+      </c>
+      <c r="F144" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="14" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>Lawyers</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>Who argued for the government in McCardle, and who represented McCardle?</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="inlineStr">
+        <is>
+          <t>Government: Lyman Trumbull, Republican Senator from Illinois (Attorney General Henry Stanbery declined to defend the Act). McCardle: David Dudley Field, brother of Justice Stephen Field.</t>
+        </is>
+      </c>
+      <c r="F145" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>How did the Court first rule on the motion to dismiss McCardle's appeal?</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>It unanimously denied the motion (the 1867 Act granted the broadest appellate jurisdiction), then heard argument in March 1868.</t>
+        </is>
+      </c>
+      <c r="F146" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="14" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>What happened Feb. 24, 1868, weeks before McCardle was argued?</t>
+        </is>
+      </c>
+      <c r="E147" s="14" t="inlineStr">
+        <is>
+          <t>The House impeached President Johnson for violating a statute limiting his power to remove officials.</t>
+        </is>
+      </c>
+      <c r="F147" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="14" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr">
+        <is>
+          <t>Repeal</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>How was the Repeal Act passed?</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="inlineStr">
+        <is>
+          <t>House Republicans inserted it into an otherwise innocuous bill on tax appeals; it passed with little debate.</t>
+        </is>
+      </c>
+      <c r="F148" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="14" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C149" s="14" t="inlineStr">
+        <is>
+          <t>Repeal</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>Congressional Globe, March 12, 1868: who questioned the repeal, who explained it, and the vote?</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="inlineStr">
+        <is>
+          <t>Senator Buckalew asked for an explanation and moved to postpone (rejected). Senator Williams of Oregon said it repealed the 1867 jurisdiction and "leaves the law of 1789 in full force." Passed 32-6.</t>
+        </is>
+      </c>
+      <c r="F149" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="14" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr">
+        <is>
+          <t>Veto</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>Johnson's veto of the Repeal Act: date and main warning?</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="inlineStr">
+        <is>
+          <t>March 25, 1868. Withdrawing jurisdiction, including over already-pending appeals, sets a precedent that "may eventually sweep away every check on arbitrary and unconstitutional legislation."</t>
+        </is>
+      </c>
+      <c r="F150" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C151" s="14" t="inlineStr">
+        <is>
+          <t>Veto</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="inlineStr">
+        <is>
+          <t>When was the veto overridden, and what did Section 2 repeal?</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="inlineStr">
+        <is>
+          <t>March 27, 1868 (15 Stat. 44). It repealed the part of the 1867 Act authorizing appeals from circuit courts to the Supreme Court, including appeals already taken.</t>
+        </is>
+      </c>
+      <c r="F151" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="14" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="D152" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (1869): who wrote it, vote, and holding?</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr">
+        <is>
+          <t>Chief Justice Salmon P. Chase, unanimous. The Court lacked jurisdiction; appeal dismissed.</t>
+        </is>
+      </c>
+      <c r="F152" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C153" s="14" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="inlineStr">
+        <is>
+          <t>McCardle: source of appellate jurisdiction?</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="inlineStr">
+        <is>
+          <t>Conferred by the Constitution, but "with such exceptions and under such regulations as Congress shall make" (Art. III, Sec. 2).</t>
+        </is>
+      </c>
+      <c r="F153" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="14" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="D154" s="14" t="inlineStr">
+        <is>
+          <t>McCardle: what principle did Durousseau v. United States establish?</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr">
+        <is>
+          <t>The Judiciary Act's affirmative description of appellate jurisdiction implies a negation of jurisdiction not described, so jurisdiction acts came to be spoken of as grants.</t>
+        </is>
+      </c>
+      <c r="F154" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="14" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="inlineStr">
+        <is>
+          <t>McCardle: on Congress's motives?</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="inlineStr">
+        <is>
+          <t>"We are not at liberty to inquire into the motives of the legislature. We can only examine into its power under the Constitution."</t>
+        </is>
+      </c>
+      <c r="F155" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="14" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>McCardle: once jurisdiction ceases, the court's only function is?</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="inlineStr">
+        <is>
+          <t>"that of announcing the fact and dismissing the cause."</t>
+        </is>
+      </c>
+      <c r="F156" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="14" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C157" s="14" t="inlineStr">
+        <is>
+          <t>Opinion</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="inlineStr">
+        <is>
+          <t>McCardle: the Court's last point about the scope of the repeal?</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="inlineStr">
+        <is>
+          <t>It removed only appeals from circuit courts under the 1867 Act. It did not affect habeas jurisdiction previously exercised.</t>
+        </is>
+      </c>
+      <c r="F157" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="14" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C158" s="14" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="D158" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte Yerger (1869): holding?</t>
+        </is>
+      </c>
+      <c r="E158" s="14" t="inlineStr">
+        <is>
+          <t>Chase, for the Court: the Supreme Court still had appellate habeas jurisdiction under the Judiciary Act of 1789 (Sec. 14), using habeas aided by certiorari. The 1868 repeal reached only the 1867 Act. Jurisdiction affirmed.</t>
+        </is>
+      </c>
+      <c r="F158" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="14" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C159" s="14" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="D159" s="14" t="inlineStr">
+        <is>
+          <t>Yerger: what interpretive maxim did Chase rely on?</t>
+        </is>
+      </c>
+      <c r="E159" s="14" t="inlineStr">
+        <is>
+          <t>"Repeals by implication are not favored."</t>
+        </is>
+      </c>
+      <c r="F159" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="14" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C160" s="14" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="D160" s="14" t="inlineStr">
+        <is>
+          <t>Yerger: how did Chase characterize the 1868 Act?</t>
+        </is>
+      </c>
+      <c r="E160" s="14" t="inlineStr">
+        <is>
+          <t>Unusual legislation "hardly to be justified except upon some imperious public exigency" that ousted the Court of a pending case; it became law within 18 days after argument concluded.</t>
+        </is>
+      </c>
+      <c r="F160" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C161" s="14" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="D161" s="14" t="inlineStr">
+        <is>
+          <t>Yerger: what did Marbury "fix," according to Chase?</t>
+        </is>
+      </c>
+      <c r="E161" s="14" t="inlineStr">
+        <is>
+          <t>That the Court's mandamus power under Sec. 13 is, under the Constitution, appellate, exercised only in revising judicial decisions. Congress cannot extend original jurisdiction beyond the cases the Constitution defines.</t>
+        </is>
+      </c>
+      <c r="F161" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="14" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="14" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (FJC essay and documents)</t>
+        </is>
+      </c>
+      <c r="C162" s="14" t="inlineStr">
+        <is>
+          <t>Aftermath</t>
+        </is>
+      </c>
+      <c r="D162" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Klein (1871): significance per FJC?</t>
+        </is>
+      </c>
+      <c r="E162" s="14" t="inlineStr">
+        <is>
+          <t>First time the Court struck down a congressional statute restricting federal jurisdiction (though it has upheld most such statutes since).</t>
+        </is>
+      </c>
+      <c r="F162" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="14" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="14" t="inlineStr">
+        <is>
+          <t>Advisory opinions: Jefferson letter (1793)</t>
+        </is>
+      </c>
+      <c r="C163" s="14" t="inlineStr">
+        <is>
+          <t>Letter</t>
+        </is>
+      </c>
+      <c r="D163" s="14" t="inlineStr">
+        <is>
+          <t>Jefferson's July 18, 1793 letter: to whom, and what prompted it?</t>
+        </is>
+      </c>
+      <c r="E163" s="14" t="inlineStr">
+        <is>
+          <t>To Chief Justice Jay and the associate justices. War among the powers of Europe raised questions in U.S. ports on treaties, the laws of nature and nations, and U.S. law.</t>
+        </is>
+      </c>
+      <c r="F163" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="14" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="14" t="inlineStr">
+        <is>
+          <t>Advisory opinions: Jefferson letter (1793)</t>
+        </is>
+      </c>
+      <c r="C164" s="14" t="inlineStr">
+        <is>
+          <t>Letter</t>
+        </is>
+      </c>
+      <c r="D164" s="14" t="inlineStr">
+        <is>
+          <t>What did Jefferson ask the justices first?</t>
+        </is>
+      </c>
+      <c r="E164" s="14" t="inlineStr">
+        <is>
+          <t>Whether the public could, with propriety, be availed of their ADVICE on these questions. If so, he would present abstract questions for them to answer or strike out.</t>
+        </is>
+      </c>
+      <c r="F164" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F164"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Con_Law_Outline_Week_8_with_Midterm_QA.xlsx
+++ b/Con_Law_Outline_Week_8_with_Midterm_QA.xlsx
@@ -23,10 +23,12 @@
     <sheet name="Week 7 Class Notes" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Week 8 Reading Notes" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Week 1 Fact Bank" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Midterm questions &amp; answers" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Week 2 Fact Bank" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Midterm questions &amp; answers" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Week 1 Fact Bank'!$A$1:$F$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Week 2 Fact Bank'!$A$1:$F$157</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -17140,6 +17142,4741 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F157"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="75" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="96" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="96" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="C1" s="96" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="D1" s="96" t="inlineStr">
+        <is>
+          <t>Question (cover this column)</t>
+        </is>
+      </c>
+      <c r="E1" s="96" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="F1" s="96" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Letter from the Justices to Washington (Aug. 8, 1793)</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>The Justices' letter of August 8, 1793: to whom, and responding to what?</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>To President George Washington, answering the "previous Question" in the letter the Secretary of State wrote at his direction on the 18th of the prior month (July 18, 1793).</t>
+        </is>
+      </c>
+      <c r="F2" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Letter from the Justices to Washington (Aug. 8, 1793)</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Signers</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Who signed the Justices' August 8, 1793 letter?</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>John Jay, James Wilson, John Blair, James Iredell ("Ja. Iredell") and William Paterson ("Wm Paterson").</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Letter from the Justices to Washington (Aug. 8, 1793)</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>What three considerations did the Justices say argue against "extrajudicially deciding" the questions?</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>(1) The lines of separation the Constitution draws between the three departments; (2) the departments being in certain respects checks on each other; (3) the Justices being "Judges of a court in the last Resort."</t>
+        </is>
+      </c>
+      <c r="F4" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Letter from the Justices to Washington (Aug. 8, 1793)</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>What textual argument did the Justices draw from the President's power to call for opinions?</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>The President's power to call on the Heads of Departments for opinions "seems to have been purposely as well as expressly limited to executive Departments" (so it does not reach the judges).</t>
+        </is>
+      </c>
+      <c r="F5" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Letter from the Justices to Washington (Aug. 8, 1793)</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Significance</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>What is the significance of the 1793 exchange of letters (Jefferson's request and the Justices' reply)?</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>The Justices declined to give the executive advice on legal questions outside a case: the origin of the federal courts' refusal to issue advisory opinions, grounded in separation of powers.</t>
+        </is>
+      </c>
+      <c r="F6" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Letter from the Justices to Washington (Aug. 8, 1793)</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Tone</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>How did the Justices close their letter to Washington?</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>They "exceedingly regret" any embarrassment to his administration but trust his "Judgment," "Prudence, Decision and Firmness" will surmount every obstacle.</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice (treatise)</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>What is the Moore's reading, and where can it be found?</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>15 Moore's Federal Practice - Civil (Matthew Bender, 3d ed., 2025), "a leading treatise," available in hardcopy in the library and electronically on LEXIS.</t>
+        </is>
+      </c>
+      <c r="F8" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice (treatise)</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Why does the professor assign the Moore's sections?</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>As an overview of standing and (possibly) an introduction to the usefulness of a treatise; students need to be familiar with treatises in general and how to find things in them.</t>
+        </is>
+      </c>
+      <c r="F9" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice (treatise)</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Which four Moore's sections are assigned, and their titles?</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>§ 101.20 Focus of Standing Inquiry Is Who May Bring Suit; § 101.22 Historically, Standing Doctrine Has Included Both Constitutional and Prudential Requirements; § 101.23 Only One Plaintiff Need Have Standing; § 101.40 Standing Requires Injury-in-Fact.</t>
+        </is>
+      </c>
+      <c r="F10" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice (treatise)</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Per the Moore's section title, how many plaintiffs in a suit need standing?</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Only one (§ 101.23 "Only One Plaintiff Need Have Standing").</t>
+        </is>
+      </c>
+      <c r="F11" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice (treatise)</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Per the Moore's section titles, what is the focus of the standing inquiry?</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>WHO may bring suit (§ 101.20).</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Citation and author of Massachusetts v. Mellon / Frothingham v. Mellon?</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>262 U.S. 447 (1923). Justice Sutherland delivered the opinion of the Court; the two cases were argued and decided together.</t>
+        </is>
+      </c>
+      <c r="F13" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>How did Massachusetts v. Mellon reach the Supreme Court?</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>As an ORIGINAL suit in the Supreme Court, brought by Massachusetts for herself and as representative of her citizens.</t>
+        </is>
+      </c>
+      <c r="F14" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>How did Frothingham v. Mellon reach the Supreme Court?</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>By appeal from the Court of Appeals of the District of Columbia, which affirmed the Supreme Court of the District's dismissal of her bill.</t>
+        </is>
+      </c>
+      <c r="F15" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Statute</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>What statute was challenged in the Mellon cases, and what did it do?</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>The Maternity Act (Act of Nov. 23, 1921, 42 Stat. 224): appropriations for five years, apportioned among States that accept it, to reduce maternal and infant mortality and protect the health of mothers and infants; a federal bureau could withhold payments for improper spending.</t>
+        </is>
+      </c>
+      <c r="F16" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Who were the defendants in the Mellon cases?</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>The Secretary of the Treasury, the Chief of the Children's Bureau (Dept. of Labor), the Surgeon General (Public Health Service) and the Commissioner of Education; the last three formed the Board of Maternity and Infant Hygiene.</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Claims</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>What did Massachusetts claim in Massachusetts v. Mellon?</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>The Act usurped local self-government reserved by the Tenth Amendment, burdened industrial States unequally, and imposed an unconstitutional option: yield reserved rights or lose its share of the money. Massachusetts had NOT accepted the Act.</t>
+        </is>
+      </c>
+      <c r="F18" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Claims</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>What did Mrs. Frothingham claim?</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>As a federal taxpayer, the appropriations would increase her future taxes and so take her property without due process of law.</t>
+        </is>
+      </c>
+      <c r="F19" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Disposition of both Mellon cases?</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Both disposed of for want of jurisdiction, without reaching the merits.</t>
+        </is>
+      </c>
+      <c r="F20" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Why were the State's powers not invaded in Massachusetts v. Mellon?</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>The statute imposed no obligation; it simply extended an option the State was free to accept or reject. Congress's purpose to tempt may be frustrated "by the simple expedient of not yielding."</t>
+        </is>
+      </c>
+      <c r="F21" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Why did Massachusetts's claim fall outside the judicial power?</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>A State party gives original jurisdiction only for proceedings "of judicial cognizance." The naked contention that Congress usurped reserved powers by mere enactment is "political and not judicial in character."</t>
+        </is>
+      </c>
+      <c r="F22" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Mellon: which earlier case, by Justice Gray, refused a State's suit to enforce its own penal judgment against a citizen of another State?</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Wisconsin v. Pelican Insurance Co., 127 U.S. 265: the courts of no country will execute the penal laws of another.</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Mellon: in which cases did the Court keep original jurisdiction over State suits, and on what bases?</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>Texas v. White, Florida v. Anderson, Alabama v. Burr (proprietary rights); Georgia v. Tennessee Copper Co. (dominion over air and soil); Missouri v. Holland (quasi-sovereign right to regulate taking of wild game); boundary disputes.</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Mellon: which cases denied State-suit jurisdiction?</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Mandamus by one State against another's Governor to surrender a fugitive (moral, not legal, duty); New Hampshire v. Louisiana / New York v. Louisiana (enforcing another State's bonds for assignors); Georgia v. Stanton (political/governmental questions).</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Mellon: why may a MUNICIPAL taxpayer sue when a federal taxpayer may not?</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>A municipal taxpayer's interest is "direct and immediate," resembling a stockholder's relation to a private corporation. A federal taxpayer's interest is shared with millions, "comparatively minute and indeterminable," and the effect on future taxation "remote, fluctuating and uncertain."</t>
+        </is>
+      </c>
+      <c r="F26" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Mellon: what consequence would follow if one federal taxpayer could sue?</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Every other taxpayer could sue over every appropriation act and statute requiring the outlay of public money; "the bare suggestion" of such a result, "with its attendant inconveniences," supports denying the suit.</t>
+        </is>
+      </c>
+      <c r="F27" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Mellon: what must the party invoking judicial review show?</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Not only that the statute is invalid but that he "has sustained or is immediately in danger of sustaining some direct injury" from its enforcement, "and not merely that he suffers in some indefinite way in common with people generally."</t>
+        </is>
+      </c>
+      <c r="F28" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Mellon: how does Sutherland describe the judicial power over unconstitutional statutes?</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>"We have no power per se to review and annul acts of Congress." It amounts to "little more than the negative power to disregard an unconstitutional enactment." In preventive relief the court enjoins not the statute's execution but the official's acts.</t>
+        </is>
+      </c>
+      <c r="F29" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Mellon's closing line about what deciding the case would mean?</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>It "would be not to decide a judicial controversy, but to assume a position of authority over the governmental acts of another and co-equal department, an authority which plainly we do not possess."</t>
+        </is>
+      </c>
+      <c r="F30" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen: citation and author?</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>392 U.S. 83 (1968). Chief Justice Warren delivered the opinion of the Court.</t>
+        </is>
+      </c>
+      <c r="F31" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>In what court did Flast v. Cohen begin?</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>The U.S. District Court for the Southern District of New York (suit to enjoin federal expenditures). The judgment below was REVERSED.</t>
+        </is>
+      </c>
+      <c r="F32" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>What statute and spending did the Flast plaintiffs challenge?</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Titles I and II of the Elementary and Secondary Education Act of 1965: federal funds used to finance instruction (reading, arithmetic, etc.) in religious schools and to buy textbooks and materials for them.</t>
+        </is>
+      </c>
+      <c r="F33" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>How many appellants were in Flast, and on what status did they rest standing?</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Seven, resting solely on their status as federal taxpayers ("each pay[s] income taxes of the United States").</t>
+        </is>
+      </c>
+      <c r="F34" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Flast footnote 1: what additional allegation did the District Court treat as irrelevant?</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>That one appellant had children attending New York public schools. Appellants made no effort to rely on it.</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Claims</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Which constitutional clauses did the Flast plaintiffs invoke?</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>The Establishment and Free Exercise Clauses of the First Amendment (compulsory taxation for religious purposes).</t>
+        </is>
+      </c>
+      <c r="F36" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>How did Flast characterize Frothingham's 45-year effect?</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>An "impenetrable barrier" to suits against Acts of Congress by individuals asserting only the interest of federal taxpayers.</t>
+        </is>
+      </c>
+      <c r="F37" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Flast: what were the competing readings of Frothingham?</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>The Government: a constitutional rule (Article III and separation of powers). Appellants: a mere policy of judicial self-restraint. The Court: the opinion "can be read to support either position." Commentators (n.6) prevailingly saw a nonconstitutional rule of self-restraint.</t>
+        </is>
+      </c>
+      <c r="F38" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Flast: what quip did the Court make about why Mrs. Frothingham lost?</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Its reasoning suggests she "was denied standing not because she was a taxpayer but because her tax bill was not large enough."</t>
+        </is>
+      </c>
+      <c r="F39" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Flast: what modern developments undercut Frothingham's policy concerns?</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>Corporate taxpayers with federal tax liabilities of hundreds of millions of dollars; and class actions and joinder under the Federal Rules of Civil Procedure, adopted after Frothingham.</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Flast: what "quality" did the Court ascribe to the words "cases" and "controversies"?</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>An "iceberg quality": surface simplicity concealing "submerged complexities which go to the very heart of our constitutional form of government."</t>
+        </is>
+      </c>
+      <c r="F41" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Justiciability</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Flast: the two limitations embodied in "cases" and "controversies"?</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>(1) Questions presented in an adversary context and in a form historically viewed as capable of judicial resolution; (2) the judiciary's role in a tripartite allocation of power, so courts do not intrude on the other branches. "Justiciability" is the term for this dual limitation.</t>
+        </is>
+      </c>
+      <c r="F42" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Flast: why look to the substantive issues when deciding standing?</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>To decide whether there is a "logical nexus between the status asserted and the claim sought to be adjudicated" (e.g., standing differs for Establishment and Free Exercise claims).</t>
+        </is>
+      </c>
+      <c r="F43" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Flast two-part nexus test: first nexus?</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>A logical link between taxpayer status and the type of enactment attacked: only exercises of congressional power under the taxing and spending clause of Art. I, § 8. Not an incidental expenditure in administering an essentially regulatory statute.</t>
+        </is>
+      </c>
+      <c r="F44" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Flast two-part nexus test: second nexus?</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>A nexus between taxpayer status and the precise nature of the infringement: the enactment exceeds SPECIFIC constitutional limitations on the taxing and spending power, not merely that it is generally beyond Art. I, § 8 powers.</t>
+        </is>
+      </c>
+      <c r="F45" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Flast: which clause is identified as a specific limit on the taxing and spending power?</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>The Establishment Clause. Whether other specific limitations exist "can be determined only in the context of future cases."</t>
+        </is>
+      </c>
+      <c r="F46" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>How did Flast reconcile its result with Frothingham?</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Frothingham met the first nexus (spending program) but not the second: she alleged Congress exceeded its general Art. I, § 8 powers and invaded State prerogatives (Tenth Amendment), and the Fifth Amendment Due Process Clause does not protect against tax increases.</t>
+        </is>
+      </c>
+      <c r="F47" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Flast holding?</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>A taxpayer has Article III standing when he alleges congressional action under the taxing and spending clause violates constitutional provisions that restrict that power; the Flast appellants satisfied both nexuses. No view on the merits.</t>
+        </is>
+      </c>
+      <c r="F48" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Flast: what does a taxpayer who fails the test seek to do?</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>"employ a federal court as a forum in which to air his generalized grievances about the conduct of government or the allocation of power in the Federal System."</t>
+        </is>
+      </c>
+      <c r="F49" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Concurrence</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Justice Douglas's concurrence in Flast?</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>He joined, but thought the test not "durable" (for reasons stated by Harlan); it would erode and lead to Frothingham's demise, so it would be wise "to be rid of Frothingham here and now."</t>
+        </is>
+      </c>
+      <c r="F50" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>Justice Harlan's dissent in Flast?</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>The end result of Frothingham was correct even though he does not accept all its reasoning; he cannot accept the substituted standing doctrine, which "rests on premises that do not withstand analysis."</t>
+        </is>
+      </c>
+      <c r="F51" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton: citation, author and lineup?</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>405 U.S. 727 (1972). Justice Stewart for the Court, joined by Burger, White and Marshall. Dissents: Douglas, Brennan, Blackmun. Powell and Rehnquist took no part.</t>
+        </is>
+      </c>
+      <c r="F52" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>Where is Mineral King, and what is its status?</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>A valley in the Sierra Nevada, Tulare County, California, adjacent to Sequoia National Park; part of Sequoia National Forest since 1926 and a national game refuge by special Act of Congress.</t>
+        </is>
+      </c>
+      <c r="F53" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club: who won the Forest Service bidding, and what did it get?</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>Walt Disney Enterprises, Inc., chosen from six bidders after a 1965 prospectus; it got a three-year permit to conduct surveys and explorations for a master plan.</t>
+        </is>
+      </c>
+      <c r="F54" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club: the final Disney plan's numbers?</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Approved January 1969: a $35 million complex for 14,000 visitors daily, on 80 acres of valley floor under a 30-year use permit; ski lifts etc. under a revocable special-use permit.</t>
+        </is>
+      </c>
+      <c r="F55" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club: what access and utility facilities would cross Sequoia National Park?</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>A 20-mile highway to be built by the State of California, and a high-voltage power line (66,000 volts, per Blackmun). Both needed Interior Department approval.</t>
+        </is>
+      </c>
+      <c r="F56" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club: when and where was suit filed, and under what statute?</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>June 1969, U.S. District Court for the Northern District of California; § 10 of the Administrative Procedure Act (5 U.S.C. § 702).</t>
+        </is>
+      </c>
+      <c r="F57" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club: what did the District Court and Ninth Circuit do?</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>After two days of hearings the District Court granted a preliminary injunction and upheld standing. The Ninth Circuit reversed, finding no allegation members were affected other than displeasure. The Supreme Court affirmed.</t>
+        </is>
+      </c>
+      <c r="F58" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>How did the Sierra Club describe itself in paragraph 3 of its complaint?</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>A California nonprofit based in San Francisco since 1892; about 78,000 members nationally, about 27,000 in the Bay Area, with "a special interest in the conservation and the sound maintenance" of parks, refuges and forests.</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>APA § 10 (5 U.S.C. § 702) text?</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>"A person suffering legal wrong because of agency action, or adversely affected or aggrieved by agency action within the meaning of a relevant statute, is entitled to judicial review thereof."</t>
+        </is>
+      </c>
+      <c r="F60" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>What test did Data Processing Service v. Camp and Barlow v. Collins set for APA standing?</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>"Injury in fact" plus an interest "arguably within the zone of interests to be protected or regulated" by the statute. Data Processing: competitors hurt by a Comptroller ruling letting banks do data processing. Barlow: tenant farmers vs. Agriculture regulations.</t>
+        </is>
+      </c>
+      <c r="F61" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club footnote 3: three things Congress cannot authorize Article III courts to do?</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>Render advisory opinions (Muskrat v. United States), entertain "friendly" suits (United States v. Johnson), or resolve "political questions" (Luther v. Borden).</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club: is aesthetic or environmental harm an injury in fact?</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>Yes, it may be; interests shared by the many are no less deserving. "But the 'injury in fact' test requires more than an injury to a cognizable interest. It requires that the party seeking review be himself among the injured."</t>
+        </is>
+      </c>
+      <c r="F63" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club: why did the Club lack standing?</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>It failed to allege that it or its members used Mineral King for any purpose, or would be affected in their activities or pastimes by the development. A mere "interest in a problem" is not enough.</t>
+        </is>
+      </c>
+      <c r="F64" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club footnote 8: what did the Wilderness Society amici assert, and why didn't it matter?</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>That the Club ran camping trips to Mineral King and members used it. These allegations weren't in the pleadings or raised below, and the Club declined to rely on individualized interest. It could still seek to amend under Rule 15.</t>
+        </is>
+      </c>
+      <c r="F65" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club: what would be undermined by allowing suits by those who "seek to do no more than vindicate their own value preferences"?</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>The goal of putting the decision to seek review "in the hands of those who have a direct stake in the outcome."</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>Justice Douglas's dissent in Sierra Club?</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>Standing should be conferred on environmental objects (inanimate objects about to be despoiled) to sue in their own name for their own preservation.</t>
+        </is>
+      </c>
+      <c r="F67" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>Justice Blackmun's dissent in Sierra Club: his opening question?</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>"Must our law be so rigid and our procedural concepts so inflexible that we render ourselves helpless when the existing methods and the traditional concepts do not quite fit...?"</t>
+        </is>
+      </c>
+      <c r="F68" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>Blackmun in Sierra Club: what does he predict, and how big was the project?</t>
+        </is>
+      </c>
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>The 35.3-million-dollar complex, "over 10 times greater than the Forest Service's suggested minimum," will proceed, opposition will recede, and Mineral King will be defaced.</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Blackmun's two alternatives in Sierra Club?</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>(1) Reverse and approve the District Court's standing and relief on condition the Club promptly amend its complaint; or (2) an "imaginative expansion" of standing to let bona fide environmental organizations like the Club litigate.</t>
+        </is>
+      </c>
+      <c r="F70" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>Blackmun in Sierra Club: the "dual permit" issue?</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>Whether the "dual permit" device avoided the 80-acre "recreation and resort" limit of 16 U.S.C. § 497 (expanded in 1956 from an old five-acre limit), an issue apparently never litigated.</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson: citation, author and lineup?</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>418 U.S. 166 (1974). Chief Justice Burger for the Court, joined by White, Blackmun, Powell and Rehnquist. Powell concurred. Dissents: Douglas; Brennan; Stewart joined by Marshall.</t>
+        </is>
+      </c>
+      <c r="F72" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>What statute and clause were at issue in Richardson?</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>The Central Intelligence Agency Act of 1949 (secret CIA expenditures) challenged under Art. I, § 9, cl. 7: "a regular Statement and Account of the Receipts and Expenditures of all public Money shall be published from time to time" (Statement and Account / Accounts Clause).</t>
+        </is>
+      </c>
+      <c r="F73" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>In what capacities did Richardson claim standing?</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>As a federal taxpayer (the question on certiorari); his complaint also called him "a member of the electorate, and a loyal citizen."</t>
+        </is>
+      </c>
+      <c r="F74" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>Richardson holding?</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>No standing; reversed. His claim fails the Flast taxpayer test and is a "generalized grievance": the impact on him is "plainly undifferentiated and 'common to all members of the public.'" (quoting Ex parte Levitt).</t>
+        </is>
+      </c>
+      <c r="F75" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>What injury did Richardson assert?</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>Without detailed CIA expenditure information he could not intelligently follow Congress and the Executive or properly fulfill his obligations as a voter.</t>
+        </is>
+      </c>
+      <c r="F76" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>Richardson: what would allowing such suits imply the Founders intended?</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>"something in the nature of an Athenian democracy or a New England town meeting to oversee the conduct of the National Government by means of lawsuits in federal courts."</t>
+        </is>
+      </c>
+      <c r="F77" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>Richardson: if no one can sue, where does the issue go?</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>To the surveillance of Congress and ultimately the political process: representatives answerable at stated periods of two, four and six years. "Lack of standing" does not impair his right to assert his views "in the political forum or at the polls."</t>
+        </is>
+      </c>
+      <c r="F78" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Concurrence</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>Justice Powell's concurrence in Richardson?</t>
+        </is>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>He would go further and abandon the Flast two-part "nexus" test (not a reliable indicator), but would not overrule Flast on its facts, since taxpayer standing in Establishment Clause cases is settled.</t>
+        </is>
+      </c>
+      <c r="F79" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>Justice Douglas's dissent in Richardson: key line?</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>"The sovereign in this Nation is the people, not the bureaucracy." Without the statement of accounts, sovereignty becomes "an empty symbol and a secret bureaucracy is allowed to run our affairs." He would affirm the Court of Appeals.</t>
+        </is>
+      </c>
+      <c r="F80" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>Justice Stewart's dissent in Richardson (joined by Marshall)?</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>Flast and Frothingham throw "very little light": Richardson didn't seek to invalidate a statute but claimed the Clause gives him a right to receive, and imposes an affirmative duty to supply, the report. The Flast nexus criteria were not "a litmus test" for all standing questions.</t>
+        </is>
+      </c>
+      <c r="F81" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>Professor's comment after Richardson: what did Halperin v. CIA hold?</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="inlineStr">
+        <is>
+          <t>A FOIA plaintiff who sought and was denied the CIA budget also lacked standing under the Statement and Account Clause; Richardson's holding covers all such challenges "whether by a mere taxpayer or by a FOIA plaintiff." 629 F.2d 144 (D.C. Cir. 1980). Prof asks: a fair interpretation?</t>
+        </is>
+      </c>
+      <c r="F82" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>Did Richardson make a FOIA request for the CIA budget?</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>No (per the professor's comment).</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons: citation, author and lineup?</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>461 U.S. 95 (1983). Justice White for the Court, joined by Burger, Powell, Rehnquist and O'Connor. Marshall dissented, joined by Brennan, Blackmun and Stevens.</t>
+        </is>
+      </c>
+      <c r="F84" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>In what court did Lyons begin, and when?</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>U.S. District Court for the Central District of California; complaint filed February 7, 1977.</t>
+        </is>
+      </c>
+      <c r="F85" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>Lyons: who were the defendants, and what happened?</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>The City of Los Angeles and four of its police officers. On October 6, 1976 at 2 a.m., officers stopped Lyons for a traffic/vehicle code violation and, without provocation, applied a chokehold, rendering him unconscious and damaging his larynx.</t>
+        </is>
+      </c>
+      <c r="F86" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>Lyons: the two chokeholds at issue?</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>The "bar arm control" hold and the "carotid-artery control" hold.</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>Lyons: what did Counts I-IV, V and VI seek?</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>I-IV: damages against the officers and City. V (the focus): a preliminary and permanent injunction barring the holds. VI: a declaration that chokeholds absent threat of deadly force are per se unconstitutional.</t>
+        </is>
+      </c>
+      <c r="F88" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>Lyons holding?</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>Lyons lacked standing to seek the injunction: past illegal choking may give standing for damages but does not establish "a real and immediate threat" he would again be stopped and illegally choked.</t>
+        </is>
+      </c>
+      <c r="F89" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>Lyons: the "incredible assertion" Lyons would have had to make?</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>That he would have another police encounter AND either (1) all LA police always choke any citizen they encounter, or (2) the City ordered or authorized officers to act in that manner.</t>
+        </is>
+      </c>
+      <c r="F90" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>Lyons: absent likelihood of future injury, Lyons is no more entitled to an injunction than whom?</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>"any other citizen of Los Angeles"; courts may not entertain claims by citizens who merely assert police practices are unconstitutional.</t>
+        </is>
+      </c>
+      <c r="F91" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>Marshall's dissent in Lyons: facts he emphasized?</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>Lyons, a 24-year-old Negro male, was stopped for a burned-out taillight, met with drawn revolvers, complained of pain from his keys, and within 5-10 seconds was choked until he blacked out; he urinated and defecated, then got a traffic citation and was released.</t>
+        </is>
+      </c>
+      <c r="F92" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>Marshall's main doctrinal objection in Lyons?</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>The majority fragments standing by imposing a separate hurdle for each form of relief. Standing turns on the plaintiff's personal stake in the dispute, not in particular remedies; damages redress past injury and an injunction reduces future risk.</t>
+        </is>
+      </c>
+      <c r="F93" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>Davis, Administrative Law Treatise (2d ed. 1983)</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>Numbers</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>Kenneth Culp Davis: how many standing cases, opinions and significant cases since 1978?</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="inlineStr">
+        <is>
+          <t>240 Supreme Court standing cases; more than 500 opinions including concurrences and dissents; 48 significant cases since 1978.</t>
+        </is>
+      </c>
+      <c r="F94" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>Davis, Administrative Law Treatise (2d ed. 1983)</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>Argument</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>Davis: the "main failure" of standing law?</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>Not that the doors are opened too much or too little, but "the inconsistency, unreliability, and inordinate complexity."</t>
+        </is>
+      </c>
+      <c r="F95" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>Davis, Administrative Law Treatise (2d ed. 1983)</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>Professor's comment after Davis: what did Thole v. U.S. Bank say, and what does the professor ask?</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>"Courts sometimes make standing law more complicated than it needs to be." 140 S.Ct. 1615, 1622 (2020). Professor asks: "Any court in particular?"</t>
+        </is>
+      </c>
+      <c r="F96" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright: citation, author and lineup?</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>468 U.S. 737 (1984). Justice O'Connor for the Court, joined by Burger, White, Powell and Rehnquist. Dissents: Brennan; Stevens joined by Blackmun. Marshall took no part.</t>
+        </is>
+      </c>
+      <c r="F97" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>Allen: what idea does the case-or-controversy requirement define for the Judicial Branch?</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>The idea of separation of powers (citing Valley Forge). "The law of Art. III standing is built on a single basic idea -- the idea of separation of powers."</t>
+        </is>
+      </c>
+      <c r="F98" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>Allen quotes Judge Bork's concurrence in which case, about doctrines clustering around Article III?</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>Vander Jagt v. O'Neill (D.C. Cir. 1983): standing, mootness, ripeness, political question relate to an idea "more than an intuition but less than a rigorous and explicit theory" about the limits on "an unelected, unrepresentative judiciary."</t>
+        </is>
+      </c>
+      <c r="F99" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>Allen: the three prudential ("judicially self-imposed") standing limits?</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>(1) General bar on raising another person's legal rights; (2) bar on adjudicating generalized grievances better addressed in the representative branches; (3) the complaint must fall within the zone of interests protected by the law invoked.</t>
+        </is>
+      </c>
+      <c r="F100" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>Allen: the constitutional core of standing?</t>
+        </is>
+      </c>
+      <c r="E101" s="14" t="inlineStr">
+        <is>
+          <t>"A plaintiff must allege personal injury fairly traceable to the defendant's allegedly unlawful conduct and likely to be redressed by the requested relief."</t>
+        </is>
+      </c>
+      <c r="F101" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>Allen: how must the injury be described (quoted terms)?</t>
+        </is>
+      </c>
+      <c r="E102" s="14" t="inlineStr">
+        <is>
+          <t>"Distinct and palpable" (Gladstone, quoting Warth), not "abstract," "conjectural" or "hypothetical" (Lyons); "fairly" traceable; relief "likely" (Simon).</t>
+        </is>
+      </c>
+      <c r="F102" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>Allen: the three questions the standing inquiry asks?</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>Is the injury too abstract to be judicially cognizable? Is the line of causation too attenuated? Is the prospect of relief from a favorable ruling too speculative?</t>
+        </is>
+      </c>
+      <c r="F103" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>Allen: federal courts may exercise power only how (Chicago &amp; Grand Trunk R. Co. v. Wellman)?</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>"in the last resort, and as a necessity."</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>Allen: how can many standing questions be answered?</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>Chiefly by comparing the complaint's allegations with those in prior standing cases (citing Lyons).</t>
+        </is>
+      </c>
+      <c r="F105" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>Warth v. Seldin, as quoted in Allen: "In essence the question of standing is..."?</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>"whether the litigant is entitled to have the court decide the merits of the dispute or of particular issues."</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife: citation and author?</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t>504 U.S. 555 (1992). Justice Scalia for the Court (Parts I, II, III-A, IV), joined by Rehnquist, White, Kennedy, Souter, Thomas; Part III-B (redressability) was a plurality (Rehnquist, White, Thomas).</t>
+        </is>
+      </c>
+      <c r="F107" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: separate opinions?</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t>Kennedy (joined by Souter) concurring in part and in the judgment; Stevens concurring in the judgment; Blackmun dissenting, with O'Connor.</t>
+        </is>
+      </c>
+      <c r="F108" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>Statute</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: what rule was challenged?</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t>A rule by the Secretary of the Interior interpreting ESA § 7(a)(2) (16 U.S.C. § 1536(a)(2)) to require consultation only for actions in the United States or on the high seas.</t>
+        </is>
+      </c>
+      <c r="F109" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>Statute</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="inlineStr">
+        <is>
+          <t>ESA § 7(a)(2) requires what?</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>Each federal agency, in consultation with the Secretary, must insure that any action it authorizes, funds or carries out is not likely to jeopardize endangered or threatened species or destroy critical habitat.</t>
+        </is>
+      </c>
+      <c r="F110" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: history of the regulation?</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t>1978: FWS and NMFS joint regulation extended § 7(a)(2) to foreign nations. Interior began reexamining it the next year; a revised regulation limiting it to the U.S. and high seas was proposed in 1983 and promulgated in 1986.</t>
+        </is>
+      </c>
+      <c r="F111" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>Procedure</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: procedural history?</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>District Court dismissed for lack of standing; Eighth Circuit reversed (divided). On remand the District Court denied the Secretary's SJ motion and granted respondents' merits motion; Eighth Circuit affirmed; cert granted. Supreme Court reversed and remanded.</t>
+        </is>
+      </c>
+      <c r="F112" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>Separation</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: what examples show "case" and "controversy" can name non-judicial matters?</t>
+        </is>
+      </c>
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t>An executive inquiry ("the Hoffa case") and a legislative dispute ("the Smoot-Hawley controversy"). Scalia also quotes Madison's Federalist No. 48 that the judiciary is described by "landmarks still less uncertain."</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: the "irreducible constitutional minimum" of standing?</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>(1) Injury in fact: invasion of a legally protected interest that is (a) concrete and particularized and (b) actual or imminent, not conjectural or hypothetical; (2) causation: fairly traceable to the defendant, not an independent third party; (3) redressability: "likely," not "speculative."</t>
+        </is>
+      </c>
+      <c r="F114" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>Lujan footnote 1: what does "particularized" mean?</t>
+        </is>
+      </c>
+      <c r="E115" s="14" t="inlineStr">
+        <is>
+          <t>"the injury must affect the plaintiff in a personal and individual way."</t>
+        </is>
+      </c>
+      <c r="F115" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: who bears the burden of standing, and how?</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>The party invoking jurisdiction; the elements are not mere pleading requirements, so each must be supported with the manner and degree of evidence required at the successive stages of litigation.</t>
+        </is>
+      </c>
+      <c r="F116" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: object of government action vs. regulation of someone else?</t>
+        </is>
+      </c>
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>If the plaintiff is the object, there is ordinarily little question of injury and redress. If the injury arises from regulation (or non-regulation) of a third party, standing is "not precluded" but "substantially more difficult" to establish.</t>
+        </is>
+      </c>
+      <c r="F117" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: Joyce Kelly's affidavit?</t>
+        </is>
+      </c>
+      <c r="E118" s="14" t="inlineStr">
+        <is>
+          <t>She traveled to Egypt in 1986, observed the traditional habitat of the endangered Nile crocodile, and intends to return; harmed by the American role in rehabilitating the Aswan High Dam and developing Egypt's Master Water Plan.</t>
+        </is>
+      </c>
+      <c r="F118" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: Amy Skilbred's affidavit and deposition?</t>
+        </is>
+      </c>
+      <c r="E119" s="14" t="inlineStr">
+        <is>
+          <t>She visited Sri Lanka in 1981 and observed habitat of the Asian elephant and leopard at the AID-funded Mahaweli project site (but saw none). Asked when she would return: "There is a civil war going on right now. I don't know. Not next year, I will say. In the future."</t>
+        </is>
+      </c>
+      <c r="F119" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: why were Kelly and Skilbred's intentions to return insufficient?</t>
+        </is>
+      </c>
+      <c r="E120" s="14" t="inlineStr">
+        <is>
+          <t>"Some day" intentions, without concrete plans or any specification of when, do not show "actual or imminent" injury. Past visits prove nothing (citing Lyons on past exposure).</t>
+        </is>
+      </c>
+      <c r="F120" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>Lujan footnote 2: why reject the dissent's "soon"?</t>
+        </is>
+      </c>
+      <c r="E121" s="14" t="inlineStr">
+        <is>
+          <t>If "soon" means imminent, a mere intent to return some day fails factually; if it means "in this lifetime," it departs from precedent. Imminence ensures injury is "certainly impending," especially where the acts making the injury happen are partly within the plaintiff's own control.</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Nexus theories</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: the "ecosystem nexus" theory and why rejected?</t>
+        </is>
+      </c>
+      <c r="E122" s="14" t="inlineStr">
+        <is>
+          <t>Anyone using any part of a "contiguous ecosystem" affected by a funded activity has standing. Rejected under National Wildlife Federation: the plaintiff must use the area affected, not an area roughly "in the vicinity."</t>
+        </is>
+      </c>
+      <c r="F122" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="14" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>Nexus theories</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: the "animal nexus" and "vocational nexus" theories?</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>Anyone interested in seeing the endangered animals anywhere, or anyone with a professional interest in them, could sue. Scalia: then anyone who sees, or keeps, Asian elephants in the Bronx Zoo could sue over Sri Lanka. "This is beyond all reason."</t>
+        </is>
+      </c>
+      <c r="F123" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: standing is not what (quoting SCRAP)?</t>
+        </is>
+      </c>
+      <c r="E124" s="14" t="inlineStr">
+        <is>
+          <t>"an ingenious academic exercise in the conceivable."</t>
+        </is>
+      </c>
+      <c r="F124" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>Redressability</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="inlineStr">
+        <is>
+          <t>Lujan Part III-B (plurality): why was redressability lacking?</t>
+        </is>
+      </c>
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>The funding agencies were not parties and arguably not bound by the Secretary's regulation (the Solicitor General repudiated that it binds them); and the agencies supply only a fraction of foreign project funding (AID gave less than 10% of Mahaweli's).</t>
+        </is>
+      </c>
+      <c r="F125" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>Redressability</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>Lujan footnote 5: response to Justice Stevens's point that agencies would follow a Supreme Court ruling?</t>
+        </is>
+      </c>
+      <c r="E126" s="14" t="inlineStr">
+        <is>
+          <t>Standing is determined as of the commencement of suit, when it could not be known the case would reach the Supreme Court.</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>Procedural injury</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>Lujan Part IV: what did the Eighth Circuit hold about "procedural injury"?</t>
+        </is>
+      </c>
+      <c r="E127" s="14" t="inlineStr">
+        <is>
+          <t>That the ESA citizen-suit provision (16 U.S.C. § 1540(g), "any person may commence a civil suit") gave all persons a procedural right to consultation. The Court rejected this "abstract, self-contained, noninstrumental 'right'" to have the Executive observe procedures.</t>
+        </is>
+      </c>
+      <c r="F127" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>Procedural injury</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="inlineStr">
+        <is>
+          <t>Lujan footnote 7: when may a procedural-rights plaintiff relax redressability and immediacy?</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>When the procedure protects his concrete interests: e.g., one living adjacent to a proposed federally licensed dam may challenge the failure to prepare an environmental impact statement, though he can't show the EIS would change the outcome and the dam is years away.</t>
+        </is>
+      </c>
+      <c r="F128" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>Procedural injury</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: which earlier generalized-grievance cases did Scalia cite?</t>
+        </is>
+      </c>
+      <c r="E129" s="14" t="inlineStr">
+        <is>
+          <t>Fairchild v. Hughes (Brandeis; challenge to the Nineteenth Amendment's ratification process); Massachusetts v. Mellon; Richardson; Allen and Valley Forge; Whitmore (citizen suit to stop an execution).</t>
+        </is>
+      </c>
+      <c r="F129" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>Procedural injury</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: which constitutional duty would Congress transfer to courts by converting the public interest into an individual right?</t>
+        </is>
+      </c>
+      <c r="E130" s="14" t="inlineStr">
+        <is>
+          <t>The President's duty to "take Care that the Laws be faithfully executed" (Art. II, § 3); courts would become "virtually continuing monitors of the wisdom and soundness of Executive action" (Allen, quoting Laird v. Tatum).</t>
+        </is>
+      </c>
+      <c r="F130" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>Procedural injury</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: what line from Marbury did Scalia quote?</t>
+        </is>
+      </c>
+      <c r="E131" s="14" t="inlineStr">
+        <is>
+          <t>"The province of the court... is, solely, to decide on the rights of individuals." Vindicating the public interest is the function of Congress and the Chief Executive.</t>
+        </is>
+      </c>
+      <c r="F131" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>Procedural injury</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: does the source of the right (Constitution vs. statute) matter?</t>
+        </is>
+      </c>
+      <c r="E132" s="14" t="inlineStr">
+        <is>
+          <t>"There is absolutely no basis for making the Article III inquiry turn on the source of the asserted right." In suits against the Government, at least, the concrete injury requirement must remain.</t>
+        </is>
+      </c>
+      <c r="F132" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>Procedural injury</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>Lujan: how did Scalia reconcile Warth/Linda R.S. ("statutes creating legal rights, the invasion of which creates standing")?</t>
+        </is>
+      </c>
+      <c r="E133" s="14" t="inlineStr">
+        <is>
+          <t>Those examples elevated concrete, de facto injuries previously inadequate in law (living in an integrated community; marketing free of competition). Broadening categories of injury differs from abandoning the requirement that the plaintiff himself be injured (Sierra Club).</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C134" s="14" t="inlineStr">
+        <is>
+          <t>Concurrence</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>Kennedy's concurrence in Lujan (with Souter)?</t>
+        </is>
+      </c>
+      <c r="E134" s="14" t="inlineStr">
+        <is>
+          <t>Agreed the affiants weren't "among the injured"; noted it "may seem trivial" to require airline tickets or a date certain but they didn't use the sites regularly; would not foreclose nexus theories in other circumstances (Japan Whaling); would not reach redressability (Part III-B).</t>
+        </is>
+      </c>
+      <c r="F134" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>Concurrence</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>Stevens's concurrence in the judgment in Lujan?</t>
+        </is>
+      </c>
+      <c r="E135" s="14" t="inlineStr">
+        <is>
+          <t>He concurred because Congress did not intend § 7(a)(2) consultation to apply abroad (the merits), but disagreed that the injury was not "imminent" or not "redressable."</t>
+        </is>
+      </c>
+      <c r="F135" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>Blackmun's dissent in Lujan: summary-judgment argument?</t>
+        </is>
+      </c>
+      <c r="E136" s="14" t="inlineStr">
+        <is>
+          <t>Respondents needed only a "genuine issue" of material fact (Rule 56(c)), which the Court never mentions; it confused the evidentiary burden (Rule 56(e)) with the standard of proof.</t>
+        </is>
+      </c>
+      <c r="F136" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>Blackmun in Lujan: on concrete plans and plane tickets?</t>
+        </is>
+      </c>
+      <c r="E137" s="14" t="inlineStr">
+        <is>
+          <t>Requiring concrete plans demands "an empty formality"; nothing prevents Kelly or Skilbred from buying plane tickets. Unlike Lyons, harm here did not depend on third parties' actions.</t>
+        </is>
+      </c>
+      <c r="F137" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>Blackmun in Lujan: "Three-Card Monte" and the $170 million point?</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="inlineStr">
+        <is>
+          <t>The Government cannot play "Three-Card Monte" with agencies' authority after the Secretary had said his rules bind them. AID's "fraction" of Mahaweli funding was $170 million, large for a country of 16 million with GNP under $6 billion (1986).</t>
+        </is>
+      </c>
+      <c r="F138" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="14" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>Blackmun's closing in Lujan?</t>
+        </is>
+      </c>
+      <c r="E139" s="14" t="inlineStr">
+        <is>
+          <t>He cannot join "a slash-and-burn expedition through the law of environmental standing," quoting Marbury: "the very essence of civil liberty certainly consists in the right of every individual to claim the protection of the laws, whenever he receives an injury."</t>
+        </is>
+      </c>
+      <c r="F139" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>Basics</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins: citation, author and lineup?</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>524 U.S. 11 (1998). Justice Breyer for the Court, joined by Rehnquist, Stevens, Kennedy, Souter and Ginsburg. Scalia dissented, joined by O'Connor and Thomas.</t>
+        </is>
+      </c>
+      <c r="F140" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins: what did the FEC decide?</t>
+        </is>
+      </c>
+      <c r="E141" s="14" t="inlineStr">
+        <is>
+          <t>That the American Israel Public Affairs Committee (AIPAC) was not a "political committee" under the Federal Election Campaign Act of 1971, so it need not disclose its membership, contributions and expenditures.</t>
+        </is>
+      </c>
+      <c r="F141" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="14" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>Who were the respondents in Akins, and what did the Court hold?</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="inlineStr">
+        <is>
+          <t>A group of voters; they had standing to challenge the FEC's determination. Remanded.</t>
+        </is>
+      </c>
+      <c r="F142" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="14" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>Akins: which of the two certiorari questions did the Court answer?</t>
+        </is>
+      </c>
+      <c r="E143" s="14" t="inlineStr">
+        <is>
+          <t>Only the first (standing). It did not decide whether a group spending over $1,000 that is not candidate-controlled and lacks the major purpose of electing candidates is a "political committee."</t>
+        </is>
+      </c>
+      <c r="F143" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="14" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr">
+        <is>
+          <t>Prudential</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>Akins: why were prudential standing requirements satisfied?</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>FECA lets "any person who believes a violation... has occurred" file a complaint (§ 437g(a)(1)) and "any party aggrieved" by dismissal petition a district court (§ 437g(a)(8)(A)); Congress meant to protect voters like respondents.</t>
+        </is>
+      </c>
+      <c r="F144" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="14" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>Akins: what was the injury in fact?</t>
+        </is>
+      </c>
+      <c r="E145" s="14" t="inlineStr">
+        <is>
+          <t>Inability to obtain information (AIPAC donor/member lists, campaign contributions and expenditures) that the statute arguably requires be made public, which would help them evaluate candidates.</t>
+        </is>
+      </c>
+      <c r="F145" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>Injury</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>Akins: precedents for informational injury?</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>Public Citizen v. Department of Justice (Federal Advisory Committee Act) and Havens Realty Corp. v. Coleman (information about housing availability).</t>
+        </is>
+      </c>
+      <c r="F146" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="14" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>Richardson</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>How did Akins distinguish Richardson?</t>
+        </is>
+      </c>
+      <c r="E147" s="14" t="inlineStr">
+        <is>
+          <t>No constitutional "logical nexus" requirement applies here; instead a statute seeks to protect individuals like respondents. And Richardson focused on taxpayer standing, not voter standing.</t>
+        </is>
+      </c>
+      <c r="F147" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="14" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr">
+        <is>
+          <t>Generalized grievance</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>Akins: when does a widely shared injury still count?</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="inlineStr">
+        <is>
+          <t>Generalized-grievance language appears where harm is both widely shared and "abstract and indefinite" (e.g., "common concern for obedience to law"). Where harm is concrete, though widely shared (mass tort, voting-rights interference), it is injury in fact.</t>
+        </is>
+      </c>
+      <c r="F148" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="14" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C149" s="14" t="inlineStr">
+        <is>
+          <t>Key phrases</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>Akins: how did the Court describe the informational injury here?</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="inlineStr">
+        <is>
+          <t>"directly related to voting, the most basic of political rights," and sufficiently concrete and specific that its being widely shared does not deprive Congress of power to authorize suit.</t>
+        </is>
+      </c>
+      <c r="F149" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="14" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr">
+        <is>
+          <t>Causation</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>Akins: does the FEC's discretion defeat traceability/redressability?</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="inlineStr">
+        <is>
+          <t>No. Even if the FEC might reach the same result lawfully, a court that finds the agency misinterpreted the law sets aside and remands, "like a new jury after a mistrial."</t>
+        </is>
+      </c>
+      <c r="F150" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C151" s="14" t="inlineStr">
+        <is>
+          <t>Enforcement</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="inlineStr">
+        <is>
+          <t>Akins: why didn't Heckler v. Chaney bar review of the FEC's non-enforcement?</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="inlineStr">
+        <is>
+          <t>Heckler held enforcement decisions traditionally "committed to agency discretion" under the APA, but FECA "explicitly indicates the contrary."</t>
+        </is>
+      </c>
+      <c r="F151" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="14" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D152" s="14" t="inlineStr">
+        <is>
+          <t>Scalia's dissent in Akins: statutory argument?</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr">
+        <is>
+          <t>FECA distinguishes "any person" who may complain from a "party aggrieved" who may sue; respondents complain not of refusal to provide information but of refusal to enforce against a third party. Constitutional doubt also counsels a narrow reading.</t>
+        </is>
+      </c>
+      <c r="F152" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C153" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="inlineStr">
+        <is>
+          <t>Scalia in Akins: timing of the citizen-suit provision?</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="inlineStr">
+        <is>
+          <t>It was enacted two years after Richardson, which gave Congress every reason to think a voter's informational interest was constitutionally inadequate.</t>
+        </is>
+      </c>
+      <c r="F153" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="14" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D154" s="14" t="inlineStr">
+        <is>
+          <t>Scalia in Akins: what did the majority reduce Richardson to, and what did he call the distinction?</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr">
+        <is>
+          <t>"from a landmark constitutional holding to a curio"; the taxpayer/voter distinction is "silly." He mocks the "unaccustomed ineptitude" of the ACLU Foundation (which litigated Richardson) for not refiling as voters.</t>
+        </is>
+      </c>
+      <c r="F154" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="14" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="inlineStr">
+        <is>
+          <t>Scalia in Akins: the tort-victim illustration?</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="inlineStr">
+        <is>
+          <t>Mass-tort and voting injuries are widely shared but particularized: "One tort victim suffers a burnt leg, another a burnt arm." A generalized grievance is undifferentiated, like Richardson's and Akins's identical lack of information.</t>
+        </is>
+      </c>
+      <c r="F155" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="14" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>Scalia in Akins: the separation-of-powers conclusion?</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="inlineStr">
+        <is>
+          <t>Letting any voter compel Executive enforcement transfers the "take Care" duty (Art. II, § 3) to the courts; Congress could authorize anyone to manage enforcement of any law requiring "the filing and public availability of a piece of paper."</t>
+        </is>
+      </c>
+      <c r="F156" s="97" t="inlineStr">
+        <is>
+          <t>Must-know</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="14" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="C157" s="14" t="inlineStr">
+        <is>
+          <t>Dissent</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="inlineStr">
+        <is>
+          <t>Scalia in Akins footnote 1: Schlesinger v. Reservists?</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="inlineStr">
+        <is>
+          <t>Decided the same day as Richardson: "the Flast nexus test is not applicable where the taxing and spending power is not challenged."</t>
+        </is>
+      </c>
+      <c r="F157" s="14" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F157"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
